--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -996,7 +996,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1146,7 +1146,7 @@
         <v>0</v>
       </c>
       <c r="AU4" s="3" t="n">
-        <v>46191.5</v>
+        <v>46191.45833333334</v>
       </c>
     </row>
     <row r="5">

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G6" t="n">

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G7" t="n">

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G6" t="n">

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G7" t="n">

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G7" t="n">

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G7" t="n">

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G7" t="n">

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G6" t="n">

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G7" t="n">

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G7" t="n">

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="O9" t="n">
         <v>3.2</v>
       </c>
       <c r="P9" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="O10" t="n">
         <v>3.2</v>
       </c>
       <c r="P10" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="O9" t="n">
         <v>3.2</v>
       </c>
       <c r="P9" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="O10" t="n">
         <v>3.2</v>
       </c>
       <c r="P10" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="O9" t="n">
         <v>3.2</v>
@@ -1847,55 +1847,55 @@
         <v>3.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="S9" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T9" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="U9" t="n">
-        <v>3</v>
+        <v>2.77</v>
       </c>
       <c r="V9" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W9" t="n">
         <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="AB9" t="n">
         <v>1.76</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="O10" t="n">
         <v>3.2</v>
       </c>
       <c r="P10" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,80 +1838,80 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="O9" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P9" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="R9" t="n">
-        <v>2.03</v>
+        <v>2.22</v>
       </c>
       <c r="S9" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T9" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="U9" t="n">
-        <v>2.77</v>
+        <v>2.9</v>
       </c>
       <c r="V9" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AB9" t="n">
         <v>1.76</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE9" t="n">
         <v>1.05</v>
       </c>
       <c r="AF9" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AK9" t="n">
         <v>1.83</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.8</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="O10" t="n">
         <v>3.2</v>
@@ -2006,55 +2006,55 @@
         <v>3.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="R10" t="n">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="S10" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T10" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="U10" t="n">
-        <v>3</v>
+        <v>2.77</v>
       </c>
       <c r="V10" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W10" t="n">
         <v>1.05</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="AB10" t="n">
         <v>1.76</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="O9" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P9" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="R9" t="n">
-        <v>2.22</v>
+        <v>2.03</v>
       </c>
       <c r="S9" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T9" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="U9" t="n">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="V9" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AB9" t="n">
         <v>1.76</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE9" t="n">
         <v>1.05</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,80 +1997,80 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="O10" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P10" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="R10" t="n">
-        <v>2.03</v>
+        <v>2.22</v>
       </c>
       <c r="S10" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T10" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="U10" t="n">
-        <v>2.77</v>
+        <v>2.9</v>
       </c>
       <c r="V10" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W10" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X10" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AB10" t="n">
         <v>1.76</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE10" t="n">
         <v>1.05</v>
       </c>
       <c r="AF10" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AK10" t="n">
         <v>1.83</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1.8</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,80 +1838,80 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="O9" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P9" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="R9" t="n">
-        <v>2.03</v>
+        <v>2.22</v>
       </c>
       <c r="S9" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T9" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="U9" t="n">
-        <v>2.77</v>
+        <v>2.9</v>
       </c>
       <c r="V9" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AB9" t="n">
         <v>1.76</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE9" t="n">
         <v>1.05</v>
       </c>
       <c r="AF9" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AK9" t="n">
         <v>1.83</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.8</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="O10" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P10" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="R10" t="n">
-        <v>2.22</v>
+        <v>2.03</v>
       </c>
       <c r="S10" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T10" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="U10" t="n">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="V10" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W10" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AB10" t="n">
         <v>1.76</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE10" t="n">
         <v>1.05</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU10"/>
+  <dimension ref="A1:AU14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1155,27 +1155,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1305,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="AU5" s="3" t="n">
-        <v>46191.54166666666</v>
+        <v>46191.45833333334</v>
       </c>
     </row>
     <row r="6">
@@ -1314,27 +1314,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1464,7 +1464,7 @@
         <v>0</v>
       </c>
       <c r="AU6" s="3" t="n">
-        <v>46191.54166666666</v>
+        <v>46191.45833333334</v>
       </c>
     </row>
     <row r="7">
@@ -1473,27 +1473,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1623,7 +1623,7 @@
         <v>0</v>
       </c>
       <c r="AU7" s="3" t="n">
-        <v>46191.54166666666</v>
+        <v>46191.45833333334</v>
       </c>
     </row>
     <row r="8">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1782,7 +1782,7 @@
         <v>0</v>
       </c>
       <c r="AU8" s="3" t="n">
-        <v>46191.58333333334</v>
+        <v>46191.45833333334</v>
       </c>
     </row>
     <row r="9">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1941,7 +1941,7 @@
         <v>0</v>
       </c>
       <c r="AU9" s="3" t="n">
-        <v>46191.875</v>
+        <v>46191.54166666666</v>
       </c>
     </row>
     <row r="10">
@@ -1950,156 +1950,792 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Georgia Erovnuli Liga</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Dinamo Tbilisi</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Samgurali</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" s="3" t="n">
+        <v>46191.54166666666</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Sweden Damallsvenskan</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Häcken W</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Rosengard Women</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" s="3" t="n">
+        <v>46191.54166666666</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Sweden Damallsvenskan</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Norrköping W</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Växjö</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" s="3" t="n">
+        <v>46191.58333333334</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>21:00</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Sport Recife</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Atlético GO</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="inlineStr">
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N10" t="n">
+      <c r="N13" t="n">
         <v>1.91</v>
       </c>
-      <c r="O10" t="n">
+      <c r="O13" t="n">
         <v>3.2</v>
       </c>
-      <c r="P10" t="n">
+      <c r="P13" t="n">
         <v>3.5</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="Q13" t="n">
         <v>2.58</v>
       </c>
-      <c r="R10" t="n">
+      <c r="R13" t="n">
         <v>2.03</v>
       </c>
-      <c r="S10" t="n">
+      <c r="S13" t="n">
         <v>1.42</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T13" t="n">
         <v>2.62</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U13" t="n">
         <v>2.77</v>
       </c>
-      <c r="V10" t="n">
+      <c r="V13" t="n">
         <v>1.37</v>
       </c>
-      <c r="W10" t="n">
+      <c r="W13" t="n">
         <v>1.05</v>
       </c>
-      <c r="X10" t="n">
+      <c r="X13" t="n">
         <v>1.04</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="Y13" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="Z13" t="n">
         <v>2.97</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AA13" t="n">
         <v>2.06</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AB13" t="n">
         <v>1.76</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AC13" t="n">
         <v>3.65</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AD13" t="n">
         <v>1.25</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AE13" t="n">
         <v>1.05</v>
       </c>
-      <c r="AF10" t="n">
+      <c r="AF13" t="n">
         <v>1.83</v>
       </c>
-      <c r="AG10" t="n">
+      <c r="AG13" t="n">
         <v>1.87</v>
       </c>
-      <c r="AH10" t="inlineStr">
+      <c r="AH13" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
+      <c r="AI13" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AJ10" t="n">
+      <c r="AJ13" t="n">
         <v>1.25</v>
       </c>
-      <c r="AK10" t="n">
+      <c r="AK13" t="n">
         <v>1.8</v>
       </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU10" s="3" t="n">
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" s="3" t="n">
+        <v>46191.875</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Universidad Chile</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="P14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" s="3" t="n">
         <v>46191.875</v>
       </c>
     </row>

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -734,10 +734,10 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -746,10 +746,10 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
@@ -758,31 +758,31 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2006,10 +2006,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2018,10 +2018,10 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
@@ -2030,31 +2030,31 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2165,10 +2165,10 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2177,10 +2177,10 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
@@ -2189,31 +2189,31 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2324,10 +2324,10 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2336,10 +2336,10 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
@@ -2348,31 +2348,31 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2498,7 +2498,7 @@
         <v>2.77</v>
       </c>
       <c r="V13" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W13" t="n">
         <v>1.05</v>
@@ -2513,19 +2513,19 @@
         <v>2.97</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="AD13" t="n">
         <v>1.25</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AF13" t="n">
         <v>1.83</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2636,16 +2636,16 @@
         <v>1.84</v>
       </c>
       <c r="O14" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P14" t="n">
-        <v>4.1</v>
+        <v>3.58</v>
       </c>
       <c r="Q14" t="n">
         <v>2.46</v>
       </c>
       <c r="R14" t="n">
-        <v>2.22</v>
+        <v>2.04</v>
       </c>
       <c r="S14" t="n">
         <v>1.41</v>
@@ -2654,10 +2654,10 @@
         <v>2.66</v>
       </c>
       <c r="U14" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="V14" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W14" t="n">
         <v>1.06</v>
@@ -2669,7 +2669,7 @@
         <v>1.28</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.9</v>
+        <v>3.33</v>
       </c>
       <c r="AA14" t="n">
         <v>2.08</v>
@@ -2681,13 +2681,13 @@
         <v>3.7</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AE14" t="n">
         <v>1.05</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AG14" t="n">
         <v>1.75</v>

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1847,10 +1847,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1859,10 +1859,10 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
@@ -1871,31 +1871,31 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2165,10 +2165,10 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2177,10 +2177,10 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
@@ -2189,31 +2189,31 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,80 +2474,80 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="O13" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P13" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="R13" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="S13" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T13" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="U13" t="n">
-        <v>2.77</v>
+        <v>2.95</v>
       </c>
       <c r="V13" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE13" t="n">
         <v>1.05</v>
       </c>
-      <c r="X13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.09</v>
-      </c>
       <c r="AF13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AK13" t="n">
         <v>1.83</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.78</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.84</v>
+        <v>1.96</v>
       </c>
       <c r="O14" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P14" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="R14" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AA14" t="n">
         <v>2.04</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="U14" t="n">
-        <v>3</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.08</v>
       </c>
       <c r="AB14" t="n">
         <v>1.76</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AE14" t="n">
         <v>1.05</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1847,10 +1847,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="R9" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1859,10 +1859,10 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="V9" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
@@ -1871,32 +1871,32 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="AC9" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG9" t="n">
         <v>1.93</v>
       </c>
-      <c r="AD9" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.84</v>
-      </c>
       <c r="AH9" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.45</v>
+        <v>2.95</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2006,10 +2006,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2018,10 +2018,10 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
@@ -2030,31 +2030,31 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2165,10 +2165,10 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2177,10 +2177,10 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
@@ -2189,31 +2189,31 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="O13" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P13" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="R13" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AA13" t="n">
         <v>2.04</v>
       </c>
-      <c r="S13" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AB13" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.54</v>
+        <v>3.34</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AE13" t="n">
         <v>1.05</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AK13" t="n">
         <v>1.83</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,80 +2633,80 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.96</v>
+        <v>1.84</v>
       </c>
       <c r="O14" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P14" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="R14" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="S14" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T14" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="U14" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="V14" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X14" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.97</v>
+        <v>3.33</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.65</v>
+        <v>3.54</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AE14" t="n">
         <v>1.05</v>
       </c>
       <c r="AF14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AK14" t="n">
         <v>1.83</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.78</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2006,10 +2006,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2018,10 +2018,10 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
@@ -2030,31 +2030,31 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2165,10 +2165,10 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2177,10 +2177,10 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
@@ -2189,31 +2189,31 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="O13" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P13" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="R13" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="S13" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T13" t="n">
-        <v>2.62</v>
+        <v>2.86</v>
       </c>
       <c r="U13" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="V13" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X13" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.97</v>
+        <v>3.35</v>
       </c>
       <c r="AA13" t="n">
         <v>2.04</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.34</v>
+        <v>3.53</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AE13" t="n">
         <v>1.05</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AK13" t="n">
         <v>1.83</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="O14" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P14" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="R14" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AA14" t="n">
         <v>2.04</v>
       </c>
-      <c r="S14" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AB14" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.54</v>
+        <v>3.34</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AE14" t="n">
         <v>1.05</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AK14" t="n">
         <v>1.83</v>

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.84</v>
+        <v>1.96</v>
       </c>
       <c r="O13" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P13" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="R13" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="S13" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="T13" t="n">
-        <v>2.86</v>
+        <v>2.62</v>
       </c>
       <c r="U13" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="V13" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W13" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.35</v>
+        <v>2.97</v>
       </c>
       <c r="AA13" t="n">
         <v>2.04</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.53</v>
+        <v>3.34</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE13" t="n">
         <v>1.05</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK13" t="n">
         <v>1.83</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="O14" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P14" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="R14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AA14" t="n">
         <v>2.03</v>
       </c>
-      <c r="S14" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.04</v>
-      </c>
       <c r="AB14" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.34</v>
+        <v>3.49</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AE14" t="n">
         <v>1.05</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AK14" t="n">
         <v>1.83</v>

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.5</v>
+        <v>5.6</v>
       </c>
       <c r="O8" t="n">
         <v>3.7</v>
       </c>
       <c r="P8" t="n">
-        <v>5.8</v>
+        <v>1.52</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1847,10 +1847,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="R9" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1859,10 +1859,10 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="V9" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
@@ -1871,31 +1871,31 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Z9" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.95</v>
+        <v>3.45</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2006,10 +2006,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="R10" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2018,10 +2018,10 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="V10" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
@@ -2030,32 +2030,32 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="AC10" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG10" t="n">
         <v>1.93</v>
       </c>
-      <c r="AD10" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.84</v>
-      </c>
       <c r="AH10" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.45</v>
+        <v>2.95</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="O4" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="P4" t="n">
-        <v>4.75</v>
+        <v>5.8</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.25</v>
+        <v>5.6</v>
       </c>
       <c r="O7" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="P7" t="n">
-        <v>2.88</v>
+        <v>1.52</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>5.6</v>
+        <v>1.7</v>
       </c>
       <c r="O8" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="P8" t="n">
-        <v>1.52</v>
+        <v>4.75</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="O4" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="P4" t="n">
-        <v>5.8</v>
+        <v>4.75</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="O5" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="P5" t="n">
-        <v>2.88</v>
+        <v>5.8</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>5.6</v>
+        <v>2.25</v>
       </c>
       <c r="O7" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="P7" t="n">
-        <v>1.52</v>
+        <v>2.88</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1847,10 +1847,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1859,10 +1859,10 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
@@ -1871,31 +1871,31 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2165,10 +2165,10 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2177,10 +2177,10 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
@@ -2189,31 +2189,31 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.96</v>
+        <v>1.84</v>
       </c>
       <c r="O13" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P13" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.58</v>
+        <v>2.45</v>
       </c>
       <c r="R13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AA13" t="n">
         <v>2.03</v>
       </c>
-      <c r="S13" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.04</v>
-      </c>
       <c r="AB13" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.34</v>
+        <v>3.49</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE13" t="n">
         <v>1.05</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK13" t="n">
         <v>1.83</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.84</v>
+        <v>1.96</v>
       </c>
       <c r="O14" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P14" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="R14" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="S14" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="T14" t="n">
-        <v>2.89</v>
+        <v>2.62</v>
       </c>
       <c r="U14" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="V14" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W14" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.38</v>
+        <v>2.97</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.49</v>
+        <v>3.34</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE14" t="n">
         <v>1.05</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK14" t="n">
         <v>1.83</v>

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="O4" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="P4" t="n">
-        <v>4.75</v>
+        <v>5.8</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="O5" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="P5" t="n">
-        <v>5.8</v>
+        <v>2.88</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="O7" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P7" t="n">
-        <v>2.88</v>
+        <v>4.75</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2006,10 +2006,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="R10" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2018,10 +2018,10 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="V10" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
@@ -2030,31 +2030,31 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Z10" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.95</v>
+        <v>3.45</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2165,10 +2165,10 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="R11" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2177,10 +2177,10 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="V11" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
@@ -2189,32 +2189,32 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="AC11" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG11" t="n">
         <v>1.93</v>
       </c>
-      <c r="AD11" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.84</v>
-      </c>
       <c r="AH11" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AK11" t="n">
-        <v>3.45</v>
+        <v>2.95</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,80 +2474,80 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.84</v>
+        <v>1.98</v>
       </c>
       <c r="O13" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P13" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="R13" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="S13" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="T13" t="n">
-        <v>2.89</v>
+        <v>2.62</v>
       </c>
       <c r="U13" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="V13" t="n">
         <v>1.37</v>
       </c>
       <c r="W13" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.38</v>
+        <v>3</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.49</v>
+        <v>3.34</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AE13" t="n">
         <v>1.05</v>
       </c>
       <c r="AF13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AK13" t="n">
         <v>1.75</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.83</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.96</v>
+        <v>1.84</v>
       </c>
       <c r="O14" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P14" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.58</v>
+        <v>2.45</v>
       </c>
       <c r="R14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AA14" t="n">
         <v>2.03</v>
       </c>
-      <c r="S14" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.04</v>
-      </c>
       <c r="AB14" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.34</v>
+        <v>3.49</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE14" t="n">
         <v>1.05</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK14" t="n">
         <v>1.83</v>

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -725,80 +725,80 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q2" t="n">
         <v>2.6</v>
       </c>
       <c r="R2" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U2" t="n">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="V2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AD2" t="n">
         <v>1.42</v>
       </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
+      <c r="AE2" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ2" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AK2" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.5</v>
+        <v>2.35</v>
       </c>
       <c r="O4" t="n">
-        <v>3.7</v>
+        <v>2.85</v>
       </c>
       <c r="P4" t="n">
-        <v>5.8</v>
+        <v>2.85</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.25</v>
+        <v>2.64</v>
       </c>
       <c r="O5" t="n">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
       <c r="P5" t="n">
-        <v>2.88</v>
+        <v>2.35</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>5.6</v>
+        <v>1.63</v>
       </c>
       <c r="O6" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="P6" t="n">
-        <v>1.52</v>
+        <v>4.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.7</v>
+        <v>8</v>
       </c>
       <c r="O7" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="P7" t="n">
-        <v>4.75</v>
+        <v>1.37</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>5.44</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>14.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,80 +1997,80 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="R10" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U10" t="n">
-        <v>1.88</v>
+        <v>2.11</v>
       </c>
       <c r="V10" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
         <v>1.09</v>
       </c>
-      <c r="Z10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.07</v>
-      </c>
       <c r="AK10" t="n">
-        <v>3.45</v>
+        <v>3.14</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2165,10 +2165,10 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2177,10 +2177,10 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
@@ -2189,31 +2189,31 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2315,61 +2315,61 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="R12" t="n">
         <v>2.33</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U12" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="V12" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z12" t="n">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC12" t="n">
         <v>2.48</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG12" t="n">
         <v>2.3</v>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="O13" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P13" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="R13" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="S13" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T13" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="U13" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="V13" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X13" t="n">
         <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z13" t="n">
-        <v>3</v>
+        <v>3.38</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.34</v>
+        <v>3.49</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF13" t="n">
         <v>1.83</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,80 +2633,80 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.84</v>
+        <v>1.98</v>
       </c>
       <c r="O14" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P14" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="R14" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="S14" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="T14" t="n">
-        <v>2.89</v>
+        <v>2.62</v>
       </c>
       <c r="U14" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="V14" t="n">
         <v>1.37</v>
       </c>
       <c r="W14" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.38</v>
+        <v>3</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.49</v>
+        <v>3.34</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AE14" t="n">
         <v>1.05</v>
       </c>
       <c r="AF14" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AK14" t="n">
         <v>1.75</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.83</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.35</v>
+        <v>8</v>
       </c>
       <c r="O4" t="n">
-        <v>2.85</v>
+        <v>4.1</v>
       </c>
       <c r="P4" t="n">
-        <v>2.85</v>
+        <v>1.37</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.16</v>
+        <v>7.9</v>
       </c>
       <c r="R4" t="n">
-        <v>1.87</v>
+        <v>2.11</v>
       </c>
       <c r="S4" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="T4" t="n">
-        <v>2.36</v>
+        <v>2.56</v>
       </c>
       <c r="U4" t="n">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="V4" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="W4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE4" t="n">
         <v>1.04</v>
       </c>
-      <c r="X4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AF4" t="n">
-        <v>1.77</v>
+        <v>2.28</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.46</v>
+        <v>1.02</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.64</v>
+        <v>2.35</v>
       </c>
       <c r="O5" t="n">
-        <v>3.24</v>
+        <v>2.85</v>
       </c>
       <c r="P5" t="n">
-        <v>2.35</v>
+        <v>2.85</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.32</v>
+        <v>3.16</v>
       </c>
       <c r="R5" t="n">
-        <v>2.08</v>
+        <v>1.87</v>
       </c>
       <c r="S5" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="T5" t="n">
-        <v>2.75</v>
+        <v>2.36</v>
       </c>
       <c r="U5" t="n">
-        <v>2.77</v>
+        <v>3.25</v>
       </c>
       <c r="V5" t="n">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="W5" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE5" t="n">
         <v>1.01</v>
       </c>
-      <c r="Y5" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AF5" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,80 +1520,80 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>8</v>
+        <v>2.64</v>
       </c>
       <c r="O7" t="n">
-        <v>4.1</v>
+        <v>3.24</v>
       </c>
       <c r="P7" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK7" t="n">
         <v>1.37</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.02</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.84</v>
+        <v>1.98</v>
       </c>
       <c r="O13" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P13" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="R13" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="S13" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T13" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="U13" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="V13" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W13" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X13" t="n">
         <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.38</v>
+        <v>3</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.49</v>
+        <v>3.34</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF13" t="n">
         <v>1.83</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="O14" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P14" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="R14" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="S14" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T14" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="U14" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="V14" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X14" t="n">
         <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z14" t="n">
-        <v>3</v>
+        <v>3.38</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.34</v>
+        <v>3.49</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF14" t="n">
         <v>1.83</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>8</v>
+        <v>1.62</v>
       </c>
       <c r="O4" t="n">
-        <v>4.1</v>
+        <v>3.35</v>
       </c>
       <c r="P4" t="n">
-        <v>1.37</v>
+        <v>5.44</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.9</v>
+        <v>2.23</v>
       </c>
       <c r="R4" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="S4" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="T4" t="n">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="U4" t="n">
-        <v>2.96</v>
+        <v>3.08</v>
       </c>
       <c r="V4" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W4" t="n">
         <v>1.05</v>
       </c>
       <c r="X4" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.97</v>
+        <v>2.78</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.28</v>
+        <v>2.07</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.02</v>
+        <v>2.09</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,25 +1202,25 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.35</v>
+        <v>1.63</v>
       </c>
       <c r="O5" t="n">
-        <v>2.85</v>
+        <v>3.3</v>
       </c>
       <c r="P5" t="n">
-        <v>2.85</v>
+        <v>4.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.16</v>
+        <v>2.3</v>
       </c>
       <c r="R5" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="S5" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="T5" t="n">
-        <v>2.36</v>
+        <v>2.41</v>
       </c>
       <c r="U5" t="n">
         <v>3.25</v>
@@ -1229,25 +1229,25 @@
         <v>1.27</v>
       </c>
       <c r="W5" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
         <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="AD5" t="n">
         <v>1.16</v>
@@ -1256,10 +1256,10 @@
         <v>1.01</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.77</v>
+        <v>2.14</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.46</v>
+        <v>2.02</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,25 +1361,25 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.63</v>
+        <v>2.35</v>
       </c>
       <c r="O6" t="n">
-        <v>3.3</v>
+        <v>2.85</v>
       </c>
       <c r="P6" t="n">
-        <v>4.7</v>
+        <v>2.85</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.3</v>
+        <v>3.16</v>
       </c>
       <c r="R6" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="S6" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="T6" t="n">
-        <v>2.41</v>
+        <v>2.36</v>
       </c>
       <c r="U6" t="n">
         <v>3.25</v>
@@ -1388,25 +1388,25 @@
         <v>1.27</v>
       </c>
       <c r="W6" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X6" t="n">
         <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="AD6" t="n">
         <v>1.16</v>
@@ -1415,10 +1415,10 @@
         <v>1.01</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.14</v>
+        <v>1.77</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.02</v>
+        <v>1.46</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.64</v>
+        <v>8</v>
       </c>
       <c r="O7" t="n">
-        <v>3.24</v>
+        <v>4.1</v>
       </c>
       <c r="P7" t="n">
-        <v>2.35</v>
+        <v>1.37</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.32</v>
+        <v>7.9</v>
       </c>
       <c r="R7" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="S7" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="T7" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="U7" t="n">
-        <v>2.77</v>
+        <v>2.96</v>
       </c>
       <c r="V7" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="W7" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.65</v>
+        <v>2.28</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.1</v>
+        <v>1.55</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.37</v>
+        <v>1.02</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.62</v>
+        <v>2.64</v>
       </c>
       <c r="O8" t="n">
-        <v>3.35</v>
+        <v>3.24</v>
       </c>
       <c r="P8" t="n">
-        <v>5.44</v>
+        <v>2.35</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.23</v>
+        <v>3.32</v>
       </c>
       <c r="R8" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="S8" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="T8" t="n">
-        <v>2.47</v>
+        <v>2.75</v>
       </c>
       <c r="U8" t="n">
-        <v>3.08</v>
+        <v>2.77</v>
       </c>
       <c r="V8" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD8" t="n">
         <v>1.3</v>
       </c>
-      <c r="W8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AE8" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.07</v>
+        <v>1.65</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.66</v>
+        <v>2.1</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.09</v>
+        <v>1.37</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="O13" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P13" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="R13" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="S13" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T13" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="U13" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="V13" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X13" t="n">
         <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z13" t="n">
-        <v>3</v>
+        <v>3.38</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.34</v>
+        <v>3.49</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF13" t="n">
         <v>1.83</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="O14" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P14" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="R14" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="S14" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T14" t="n">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="U14" t="n">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="V14" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W14" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.38</v>
+        <v>3.13</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.49</v>
+        <v>3.34</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF14" t="n">
         <v>1.83</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.62</v>
+        <v>2.64</v>
       </c>
       <c r="O4" t="n">
-        <v>3.35</v>
+        <v>3.24</v>
       </c>
       <c r="P4" t="n">
-        <v>5.44</v>
+        <v>2.35</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.23</v>
+        <v>3.32</v>
       </c>
       <c r="R4" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="S4" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="T4" t="n">
-        <v>2.47</v>
+        <v>2.75</v>
       </c>
       <c r="U4" t="n">
-        <v>3.08</v>
+        <v>2.77</v>
       </c>
       <c r="V4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD4" t="n">
         <v>1.3</v>
       </c>
-      <c r="W4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AE4" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.07</v>
+        <v>1.65</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.66</v>
+        <v>2.1</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.09</v>
+        <v>1.37</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.63</v>
+        <v>8</v>
       </c>
       <c r="O5" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="P5" t="n">
-        <v>4.7</v>
+        <v>1.37</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.3</v>
+        <v>7.9</v>
       </c>
       <c r="R5" t="n">
-        <v>1.98</v>
+        <v>2.11</v>
       </c>
       <c r="S5" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="T5" t="n">
-        <v>2.41</v>
+        <v>2.56</v>
       </c>
       <c r="U5" t="n">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="V5" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="W5" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X5" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.62</v>
+        <v>2.97</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.15</v>
+        <v>3.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.02</v>
+        <v>1.02</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,25 +1361,25 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.35</v>
+        <v>1.63</v>
       </c>
       <c r="O6" t="n">
-        <v>2.85</v>
+        <v>3.3</v>
       </c>
       <c r="P6" t="n">
-        <v>2.85</v>
+        <v>4.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.16</v>
+        <v>2.3</v>
       </c>
       <c r="R6" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="S6" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="T6" t="n">
-        <v>2.36</v>
+        <v>2.41</v>
       </c>
       <c r="U6" t="n">
         <v>3.25</v>
@@ -1388,25 +1388,25 @@
         <v>1.27</v>
       </c>
       <c r="W6" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X6" t="n">
         <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="AD6" t="n">
         <v>1.16</v>
@@ -1415,10 +1415,10 @@
         <v>1.01</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.77</v>
+        <v>2.14</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.46</v>
+        <v>2.02</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>8</v>
+        <v>1.62</v>
       </c>
       <c r="O7" t="n">
-        <v>4.1</v>
+        <v>3.35</v>
       </c>
       <c r="P7" t="n">
-        <v>1.37</v>
+        <v>5.44</v>
       </c>
       <c r="Q7" t="n">
-        <v>7.9</v>
+        <v>2.23</v>
       </c>
       <c r="R7" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="T7" t="n">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="U7" t="n">
-        <v>2.96</v>
+        <v>3.08</v>
       </c>
       <c r="V7" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W7" t="n">
         <v>1.05</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.97</v>
+        <v>2.78</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.28</v>
+        <v>2.07</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.02</v>
+        <v>2.09</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.64</v>
+        <v>2.35</v>
       </c>
       <c r="O8" t="n">
-        <v>3.24</v>
+        <v>2.85</v>
       </c>
       <c r="P8" t="n">
-        <v>2.35</v>
+        <v>2.85</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.32</v>
+        <v>3.16</v>
       </c>
       <c r="R8" t="n">
-        <v>2.08</v>
+        <v>1.87</v>
       </c>
       <c r="S8" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="T8" t="n">
-        <v>2.75</v>
+        <v>2.36</v>
       </c>
       <c r="U8" t="n">
-        <v>2.77</v>
+        <v>3.25</v>
       </c>
       <c r="V8" t="n">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE8" t="n">
         <v>1.01</v>
       </c>
-      <c r="Y8" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AF8" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="O13" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P13" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="R13" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="S13" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T13" t="n">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="U13" t="n">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="V13" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W13" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.38</v>
+        <v>3.13</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.49</v>
+        <v>3.34</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF13" t="n">
         <v>1.83</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="O14" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P14" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="S14" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T14" t="n">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="U14" t="n">
-        <v>2.77</v>
+        <v>2.9</v>
       </c>
       <c r="V14" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X14" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.13</v>
+        <v>3.38</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.34</v>
+        <v>3.49</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF14" t="n">
         <v>1.83</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -725,31 +725,31 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="O2" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P2" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="R2" t="n">
         <v>2.25</v>
       </c>
       <c r="S2" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T2" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U2" t="n">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="V2" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="W2" t="n">
         <v>1.12</v>
@@ -758,22 +758,22 @@
         <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AE2" t="n">
         <v>1.13</v>
@@ -782,7 +782,7 @@
         <v>1.57</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1052,10 +1052,10 @@
         <v>2.35</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="R4" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S4" t="n">
         <v>1.36</v>
@@ -1064,16 +1064,16 @@
         <v>2.75</v>
       </c>
       <c r="U4" t="n">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="V4" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="W4" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y4" t="n">
         <v>1.26</v>
@@ -1082,25 +1082,25 @@
         <v>3.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE4" t="n">
         <v>1.08</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>8</v>
+        <v>1.63</v>
       </c>
       <c r="O5" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="P5" t="n">
-        <v>1.37</v>
+        <v>4.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.9</v>
+        <v>2.3</v>
       </c>
       <c r="R5" t="n">
-        <v>2.11</v>
+        <v>1.98</v>
       </c>
       <c r="S5" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="T5" t="n">
-        <v>2.56</v>
+        <v>2.41</v>
       </c>
       <c r="U5" t="n">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="V5" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="W5" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.97</v>
+        <v>2.62</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.5</v>
+        <v>4.15</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.02</v>
+        <v>2.02</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="O6" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P6" t="n">
-        <v>4.7</v>
+        <v>5.44</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="R6" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="T6" t="n">
-        <v>2.41</v>
+        <v>2.47</v>
       </c>
       <c r="U6" t="n">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="V6" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W6" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X6" t="n">
         <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.15</v>
+        <v>3.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.02</v>
+        <v>2.09</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.62</v>
+        <v>8</v>
       </c>
       <c r="O7" t="n">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="P7" t="n">
-        <v>5.44</v>
+        <v>1.37</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.23</v>
+        <v>7.9</v>
       </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="S7" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="T7" t="n">
-        <v>2.47</v>
+        <v>2.56</v>
       </c>
       <c r="U7" t="n">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="V7" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W7" t="n">
         <v>1.05</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.78</v>
+        <v>2.97</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.07</v>
+        <v>2.28</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.09</v>
+        <v>1.02</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.1</v>
+        <v>1.78</v>
       </c>
       <c r="O9" t="n">
-        <v>7.3</v>
+        <v>3.6</v>
       </c>
       <c r="P9" t="n">
-        <v>14.2</v>
+        <v>4.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.55</v>
+        <v>2.32</v>
       </c>
       <c r="R9" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="T9" t="n">
         <v>3</v>
       </c>
-      <c r="S9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="T9" t="n">
-        <v>4.5</v>
-      </c>
       <c r="U9" t="n">
-        <v>1.88</v>
+        <v>2.65</v>
       </c>
       <c r="V9" t="n">
-        <v>1.7</v>
+        <v>1.42</v>
       </c>
       <c r="W9" t="n">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="Z9" t="n">
-        <v>6</v>
+        <v>3.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.36</v>
+        <v>1.85</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.75</v>
+        <v>1.85</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.93</v>
+        <v>3.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.72</v>
+        <v>1.31</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.29</v>
+        <v>1.08</v>
       </c>
       <c r="AF9" t="n">
         <v>1.8</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.45</v>
+        <v>1.95</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,37 +1997,37 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="O10" t="n">
-        <v>5.2</v>
+        <v>5.65</v>
       </c>
       <c r="P10" t="n">
-        <v>8.199999999999999</v>
+        <v>10.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="R10" t="n">
-        <v>2.63</v>
+        <v>2.73</v>
       </c>
       <c r="S10" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T10" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U10" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="V10" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="W10" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
         <v>1.12</v>
@@ -2036,25 +2036,25 @@
         <v>5.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.14</v>
+        <v>3.45</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="O12" t="n">
-        <v>3.54</v>
+        <v>3.35</v>
       </c>
       <c r="P12" t="n">
-        <v>3.14</v>
+        <v>3.51</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
       <c r="R12" t="n">
-        <v>2.33</v>
+        <v>2.18</v>
       </c>
       <c r="S12" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="T12" t="n">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="U12" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="V12" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AF12" t="n">
         <v>1.5</v>
       </c>
-      <c r="W12" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AG12" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,55 +2474,55 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="O13" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P13" t="n">
-        <v>3.5</v>
+        <v>4.19</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="R13" t="n">
         <v>2.1</v>
       </c>
       <c r="S13" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="T13" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="U13" t="n">
-        <v>2.77</v>
+        <v>2.94</v>
       </c>
       <c r="V13" t="n">
         <v>1.37</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X13" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.04</v>
+        <v>1.92</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.34</v>
+        <v>3.65</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE13" t="n">
         <v>1.05</v>
@@ -2531,7 +2531,7 @@
         <v>1.83</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="O14" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P14" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="R14" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="S14" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T14" t="n">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="U14" t="n">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="V14" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W14" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.38</v>
+        <v>3.13</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.49</v>
+        <v>3.34</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF14" t="n">
         <v>1.83</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="O5" t="n">
         <v>3.3</v>
       </c>
       <c r="P5" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="R5" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="S5" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="T5" t="n">
-        <v>2.41</v>
+        <v>2.47</v>
       </c>
       <c r="U5" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="V5" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W5" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X5" t="n">
         <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.62</v>
+        <v>2.79</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.15</v>
+        <v>3.82</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.24</v>
+        <v>1.09</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,31 +1361,31 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.62</v>
+        <v>2.35</v>
       </c>
       <c r="O6" t="n">
-        <v>3.35</v>
+        <v>2.9</v>
       </c>
       <c r="P6" t="n">
-        <v>5.44</v>
+        <v>2.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.23</v>
+        <v>2.8</v>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S6" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="T6" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="U6" t="n">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="V6" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="W6" t="n">
         <v>1.05</v>
@@ -1394,31 +1394,31 @@
         <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.07</v>
+        <v>1.91</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.09</v>
+        <v>1.46</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="O7" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="P7" t="n">
         <v>1.37</v>
@@ -1532,7 +1532,7 @@
         <v>7.9</v>
       </c>
       <c r="R7" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="S7" t="n">
         <v>1.42</v>
@@ -1541,13 +1541,13 @@
         <v>2.56</v>
       </c>
       <c r="U7" t="n">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="V7" t="n">
         <v>1.32</v>
       </c>
       <c r="W7" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X7" t="n">
         <v>1.02</v>
@@ -1559,25 +1559,25 @@
         <v>2.97</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="AD7" t="n">
         <v>1.22</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.28</v>
+        <v>1.94</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.17</v>
+        <v>2.3</v>
       </c>
       <c r="AK7" t="n">
         <v>1.02</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.35</v>
+        <v>1.67</v>
       </c>
       <c r="O8" t="n">
-        <v>2.85</v>
+        <v>3.25</v>
       </c>
       <c r="P8" t="n">
-        <v>2.85</v>
+        <v>4.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.16</v>
+        <v>2.3</v>
       </c>
       <c r="R8" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="T8" t="n">
-        <v>2.36</v>
+        <v>2.6</v>
       </c>
       <c r="U8" t="n">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="V8" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W8" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.83</v>
+        <v>1.64</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.31</v>
+        <v>1.1</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.46</v>
+        <v>2.02</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,80 +1838,80 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.78</v>
+        <v>1.2</v>
       </c>
       <c r="O9" t="n">
-        <v>3.6</v>
+        <v>5.65</v>
       </c>
       <c r="P9" t="n">
-        <v>4.2</v>
+        <v>10.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.32</v>
+        <v>1.57</v>
       </c>
       <c r="R9" t="n">
-        <v>2.23</v>
+        <v>2.73</v>
       </c>
       <c r="S9" t="n">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="T9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U9" t="n">
-        <v>2.65</v>
+        <v>2.1</v>
       </c>
       <c r="V9" t="n">
-        <v>1.42</v>
+        <v>1.65</v>
       </c>
       <c r="W9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
         <v>1.07</v>
       </c>
-      <c r="X9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AK9" t="n">
-        <v>1.95</v>
+        <v>3.45</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,31 +1997,31 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="O10" t="n">
-        <v>5.65</v>
+        <v>5.35</v>
       </c>
       <c r="P10" t="n">
-        <v>10.9</v>
+        <v>8.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="R10" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="S10" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T10" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U10" t="n">
         <v>2.1</v>
       </c>
       <c r="V10" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W10" t="n">
         <v>1.14</v>
@@ -2030,7 +2030,7 @@
         <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z10" t="n">
         <v>5.2</v>
@@ -2039,22 +2039,22 @@
         <v>1.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,80 +2156,80 @@
         </is>
       </c>
       <c r="N11" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y11" t="n">
         <v>1.26</v>
       </c>
-      <c r="O11" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="P11" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.11</v>
-      </c>
       <c r="Z11" t="n">
-        <v>5.2</v>
+        <v>3.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.52</v>
+        <v>1.85</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.64</v>
+        <v>1.31</v>
       </c>
       <c r="AE11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
         <v>1.24</v>
       </c>
-      <c r="AF11" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AK11" t="n">
-        <v>3.4</v>
+        <v>1.95</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,55 +2474,55 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="O13" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P13" t="n">
-        <v>4.19</v>
+        <v>3.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="R13" t="n">
         <v>2.1</v>
       </c>
       <c r="S13" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="T13" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="U13" t="n">
-        <v>2.94</v>
+        <v>2.77</v>
       </c>
       <c r="V13" t="n">
         <v>1.37</v>
       </c>
       <c r="W13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X13" t="n">
         <v>1.07</v>
       </c>
-      <c r="X13" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y13" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.65</v>
+        <v>3.34</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE13" t="n">
         <v>1.05</v>
@@ -2531,7 +2531,7 @@
         <v>1.83</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,55 +2633,55 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="O14" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P14" t="n">
-        <v>3.5</v>
+        <v>4.19</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="R14" t="n">
         <v>2.1</v>
       </c>
       <c r="S14" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="T14" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="U14" t="n">
-        <v>2.77</v>
+        <v>2.94</v>
       </c>
       <c r="V14" t="n">
         <v>1.37</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X14" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.04</v>
+        <v>1.92</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.34</v>
+        <v>3.65</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE14" t="n">
         <v>1.05</v>
@@ -2690,7 +2690,7 @@
         <v>1.83</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.64</v>
+        <v>1.61</v>
       </c>
       <c r="O4" t="n">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="P4" t="n">
-        <v>2.35</v>
+        <v>5</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.4</v>
+        <v>2.25</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S4" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="T4" t="n">
-        <v>2.75</v>
+        <v>2.47</v>
       </c>
       <c r="U4" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="V4" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="W4" t="n">
         <v>1.06</v>
       </c>
       <c r="X4" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.2</v>
+        <v>2.79</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.88</v>
+        <v>2.16</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.81</v>
+        <v>1.62</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.14</v>
+        <v>3.82</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.69</v>
+        <v>2.05</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.97</v>
+        <v>1.67</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.29</v>
+        <v>1.09</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.4</v>
+        <v>2.05</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.61</v>
+        <v>2.35</v>
       </c>
       <c r="O5" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="P5" t="n">
-        <v>5</v>
+        <v>2.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="R5" t="n">
         <v>2.05</v>
       </c>
       <c r="S5" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="T5" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="U5" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="V5" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="W5" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X5" t="n">
         <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.79</v>
+        <v>2.88</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.82</v>
+        <v>4.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.05</v>
+        <v>1.46</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,37 +1361,37 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.35</v>
+        <v>1.67</v>
       </c>
       <c r="O6" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="P6" t="n">
-        <v>2.9</v>
+        <v>4.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="R6" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T6" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="U6" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="V6" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="W6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X6" t="n">
         <v>1.05</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
         <v>1.36</v>
@@ -1403,22 +1403,22 @@
         <v>2.25</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.78</v>
+        <v>1.64</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.33</v>
+        <v>1.1</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.46</v>
+        <v>2.02</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.67</v>
+        <v>2.64</v>
       </c>
       <c r="O8" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="P8" t="n">
-        <v>4.8</v>
+        <v>2.35</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="R8" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S8" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T8" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="U8" t="n">
-        <v>3.18</v>
+        <v>2.75</v>
       </c>
       <c r="V8" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="W8" t="n">
         <v>1.06</v>
       </c>
       <c r="X8" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.25</v>
+        <v>1.88</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.5</v>
+        <v>3.14</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.1</v>
+        <v>1.69</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.64</v>
+        <v>1.97</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.02</v>
+        <v>1.4</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,31 +1838,31 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="O9" t="n">
-        <v>5.65</v>
+        <v>5.35</v>
       </c>
       <c r="P9" t="n">
-        <v>10.9</v>
+        <v>8.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="R9" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="S9" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T9" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U9" t="n">
         <v>2.1</v>
       </c>
       <c r="V9" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W9" t="n">
         <v>1.14</v>
@@ -1871,7 +1871,7 @@
         <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z9" t="n">
         <v>5.2</v>
@@ -1880,22 +1880,22 @@
         <v>1.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,80 +1997,80 @@
         </is>
       </c>
       <c r="N10" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y10" t="n">
         <v>1.26</v>
       </c>
-      <c r="O10" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="P10" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.11</v>
-      </c>
       <c r="Z10" t="n">
-        <v>5.2</v>
+        <v>3.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.52</v>
+        <v>1.85</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.64</v>
+        <v>1.31</v>
       </c>
       <c r="AE10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
         <v>1.24</v>
       </c>
-      <c r="AF10" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AK10" t="n">
-        <v>3.4</v>
+        <v>1.95</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,80 +2156,80 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.78</v>
+        <v>1.2</v>
       </c>
       <c r="O11" t="n">
-        <v>3.6</v>
+        <v>5.65</v>
       </c>
       <c r="P11" t="n">
-        <v>4.2</v>
+        <v>10.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.32</v>
+        <v>1.57</v>
       </c>
       <c r="R11" t="n">
-        <v>2.23</v>
+        <v>2.73</v>
       </c>
       <c r="S11" t="n">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="T11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U11" t="n">
-        <v>2.65</v>
+        <v>2.1</v>
       </c>
       <c r="V11" t="n">
-        <v>1.42</v>
+        <v>1.65</v>
       </c>
       <c r="W11" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
         <v>1.07</v>
       </c>
-      <c r="X11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AK11" t="n">
-        <v>1.95</v>
+        <v>3.45</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,55 +2474,55 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="O13" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P13" t="n">
-        <v>3.5</v>
+        <v>4.19</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="R13" t="n">
         <v>2.1</v>
       </c>
       <c r="S13" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="T13" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="U13" t="n">
-        <v>2.77</v>
+        <v>2.94</v>
       </c>
       <c r="V13" t="n">
         <v>1.37</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X13" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.04</v>
+        <v>1.92</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.34</v>
+        <v>3.65</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE13" t="n">
         <v>1.05</v>
@@ -2531,7 +2531,7 @@
         <v>1.83</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,55 +2633,55 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="O14" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P14" t="n">
-        <v>4.19</v>
+        <v>3.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="R14" t="n">
         <v>2.1</v>
       </c>
       <c r="S14" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="T14" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="U14" t="n">
-        <v>2.94</v>
+        <v>2.77</v>
       </c>
       <c r="V14" t="n">
         <v>1.37</v>
       </c>
       <c r="W14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X14" t="n">
         <v>1.07</v>
       </c>
-      <c r="X14" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y14" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.65</v>
+        <v>3.34</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE14" t="n">
         <v>1.05</v>
@@ -2690,7 +2690,7 @@
         <v>1.83</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.67</v>
+        <v>2.64</v>
       </c>
       <c r="O6" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="P6" t="n">
-        <v>4.8</v>
+        <v>2.35</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S6" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T6" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="U6" t="n">
-        <v>3.18</v>
+        <v>2.75</v>
       </c>
       <c r="V6" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="W6" t="n">
         <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.25</v>
+        <v>1.88</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.5</v>
+        <v>3.14</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.1</v>
+        <v>1.69</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.64</v>
+        <v>1.97</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.02</v>
+        <v>1.4</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.64</v>
+        <v>1.67</v>
       </c>
       <c r="O8" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="P8" t="n">
-        <v>2.35</v>
+        <v>4.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T8" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="U8" t="n">
-        <v>2.75</v>
+        <v>3.18</v>
       </c>
       <c r="V8" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="W8" t="n">
         <v>1.06</v>
       </c>
       <c r="X8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE8" t="n">
         <v>1.02</v>
       </c>
-      <c r="Y8" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AF8" t="n">
-        <v>1.69</v>
+        <v>2.1</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.97</v>
+        <v>1.64</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.4</v>
+        <v>2.02</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,80 +1838,80 @@
         </is>
       </c>
       <c r="N9" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y9" t="n">
         <v>1.26</v>
       </c>
-      <c r="O9" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="P9" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.11</v>
-      </c>
       <c r="Z9" t="n">
-        <v>5.2</v>
+        <v>3.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.52</v>
+        <v>1.85</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.64</v>
+        <v>1.31</v>
       </c>
       <c r="AE9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
         <v>1.24</v>
       </c>
-      <c r="AF9" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AK9" t="n">
-        <v>3.4</v>
+        <v>1.95</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,80 +1997,80 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.78</v>
+        <v>1.26</v>
       </c>
       <c r="O10" t="n">
-        <v>3.6</v>
+        <v>5.35</v>
       </c>
       <c r="P10" t="n">
-        <v>4.2</v>
+        <v>8.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.32</v>
+        <v>1.65</v>
       </c>
       <c r="R10" t="n">
-        <v>2.23</v>
+        <v>2.7</v>
       </c>
       <c r="S10" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="T10" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="U10" t="n">
-        <v>2.65</v>
+        <v>2.1</v>
       </c>
       <c r="V10" t="n">
-        <v>1.42</v>
+        <v>1.64</v>
       </c>
       <c r="W10" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.26</v>
+        <v>1.11</v>
       </c>
       <c r="Z10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK10" t="n">
         <v>3.4</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1.95</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,55 +2474,55 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="O13" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P13" t="n">
-        <v>4.19</v>
+        <v>3.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="R13" t="n">
         <v>2.1</v>
       </c>
       <c r="S13" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="T13" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="U13" t="n">
-        <v>2.94</v>
+        <v>2.77</v>
       </c>
       <c r="V13" t="n">
         <v>1.37</v>
       </c>
       <c r="W13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X13" t="n">
         <v>1.07</v>
       </c>
-      <c r="X13" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y13" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.65</v>
+        <v>3.34</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE13" t="n">
         <v>1.05</v>
@@ -2531,7 +2531,7 @@
         <v>1.83</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,55 +2633,55 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="O14" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P14" t="n">
-        <v>3.5</v>
+        <v>4.19</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="R14" t="n">
         <v>2.1</v>
       </c>
       <c r="S14" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="T14" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="U14" t="n">
-        <v>2.77</v>
+        <v>2.94</v>
       </c>
       <c r="V14" t="n">
         <v>1.37</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X14" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.04</v>
+        <v>1.92</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.34</v>
+        <v>3.65</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE14" t="n">
         <v>1.05</v>
@@ -2690,7 +2690,7 @@
         <v>1.83</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.03</v>
+        <v>2.09</v>
       </c>
       <c r="O2" t="n">
-        <v>3.45</v>
+        <v>3.46</v>
       </c>
       <c r="P2" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="Q2" t="n">
         <v>2.45</v>
@@ -740,19 +740,19 @@
         <v>2.25</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T2" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="U2" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="V2" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="W2" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X2" t="n">
         <v>1.01</v>
@@ -761,13 +761,13 @@
         <v>1.18</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.82</v>
+        <v>3.6</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="AC2" t="n">
         <v>2.75</v>
@@ -779,10 +779,10 @@
         <v>1.13</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>1.25</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.92</v>
+        <v>3.21</v>
       </c>
       <c r="O3" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="P3" t="n">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
       <c r="R3" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="S3" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T3" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="U3" t="n">
         <v>2.9</v>
       </c>
       <c r="V3" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W3" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE3" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y3" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AF3" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.29</v>
+        <v>1.58</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,31 +1043,31 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.61</v>
+        <v>6.5</v>
       </c>
       <c r="O4" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="P4" t="n">
-        <v>5</v>
+        <v>1.39</v>
       </c>
       <c r="Q4" t="n">
+        <v>8</v>
+      </c>
+      <c r="R4" t="n">
         <v>2.25</v>
       </c>
-      <c r="R4" t="n">
-        <v>2.05</v>
-      </c>
       <c r="S4" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="T4" t="n">
-        <v>2.47</v>
+        <v>2.75</v>
       </c>
       <c r="U4" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="V4" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W4" t="n">
         <v>1.06</v>
@@ -1076,31 +1076,31 @@
         <v>1.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.79</v>
+        <v>3.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.82</v>
+        <v>3.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK4" t="n">
         <v>1.09</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>2.05</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.35</v>
+        <v>1.67</v>
       </c>
       <c r="O5" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="P5" t="n">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.8</v>
+        <v>2.31</v>
       </c>
       <c r="R5" t="n">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="S5" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="T5" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="U5" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="V5" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="W5" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X5" t="n">
         <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="AA5" t="n">
         <v>2.25</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.2</v>
+        <v>3.92</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.46</v>
+        <v>2.05</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,31 +1361,31 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.64</v>
+        <v>1.55</v>
       </c>
       <c r="O6" t="n">
-        <v>3.24</v>
+        <v>3.55</v>
       </c>
       <c r="P6" t="n">
-        <v>2.35</v>
+        <v>5.78</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="R6" t="n">
         <v>2.1</v>
       </c>
       <c r="S6" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T6" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="U6" t="n">
-        <v>2.75</v>
+        <v>3.15</v>
       </c>
       <c r="V6" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="W6" t="n">
         <v>1.06</v>
@@ -1394,31 +1394,31 @@
         <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.2</v>
+        <v>2.74</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.88</v>
+        <v>2.25</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.81</v>
+        <v>1.62</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.14</v>
+        <v>4.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.69</v>
+        <v>2.15</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.97</v>
+        <v>1.61</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>6.5</v>
+        <v>2.3</v>
       </c>
       <c r="O7" t="n">
-        <v>3.9</v>
+        <v>2.96</v>
       </c>
       <c r="P7" t="n">
-        <v>1.37</v>
+        <v>2.88</v>
       </c>
       <c r="Q7" t="n">
-        <v>7.9</v>
+        <v>3.12</v>
       </c>
       <c r="R7" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="T7" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="U7" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="V7" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="W7" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE7" t="n">
         <v>1.02</v>
       </c>
-      <c r="Y7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.09</v>
-      </c>
       <c r="AF7" t="n">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>2.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.02</v>
+        <v>1.47</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.67</v>
+        <v>2.45</v>
       </c>
       <c r="O8" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="P8" t="n">
-        <v>4.8</v>
+        <v>2.26</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="R8" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S8" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T8" t="n">
-        <v>2.6</v>
+        <v>2.71</v>
       </c>
       <c r="U8" t="n">
-        <v>3.18</v>
+        <v>2.88</v>
       </c>
       <c r="V8" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="W8" t="n">
         <v>1.06</v>
       </c>
       <c r="X8" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.88</v>
+        <v>3.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.1</v>
+        <v>1.58</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.64</v>
+        <v>2.12</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.02</v>
+        <v>1.4</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,65 +1838,65 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.78</v>
+        <v>1.21</v>
       </c>
       <c r="O9" t="n">
-        <v>3.6</v>
+        <v>5.95</v>
       </c>
       <c r="P9" t="n">
-        <v>4.2</v>
+        <v>7.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.32</v>
+        <v>1.57</v>
       </c>
       <c r="R9" t="n">
-        <v>2.23</v>
+        <v>2.88</v>
       </c>
       <c r="S9" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="T9" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="U9" t="n">
-        <v>2.65</v>
+        <v>2.05</v>
       </c>
       <c r="V9" t="n">
-        <v>1.42</v>
+        <v>1.67</v>
       </c>
       <c r="W9" t="n">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.26</v>
+        <v>1.11</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.4</v>
+        <v>5.5</v>
       </c>
       <c r="AA9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG9" t="n">
         <v>1.85</v>
       </c>
-      <c r="AB9" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.92</v>
-      </c>
       <c r="AH9" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.95</v>
+        <v>3.5</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="O10" t="n">
-        <v>5.35</v>
+        <v>5.65</v>
       </c>
       <c r="P10" t="n">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="R10" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="S10" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="T10" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U10" t="n">
         <v>2.1</v>
       </c>
       <c r="V10" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W10" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X10" t="n">
         <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AA10" t="n">
         <v>1.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,80 +2156,80 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="O11" t="n">
-        <v>5.65</v>
+        <v>3.48</v>
       </c>
       <c r="P11" t="n">
-        <v>10.9</v>
+        <v>4.42</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.57</v>
+        <v>2.26</v>
       </c>
       <c r="R11" t="n">
-        <v>2.73</v>
+        <v>2.25</v>
       </c>
       <c r="S11" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="T11" t="n">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="U11" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="V11" t="n">
-        <v>1.65</v>
+        <v>1.36</v>
       </c>
       <c r="W11" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.2</v>
+        <v>3.34</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.12</v>
+        <v>3.05</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.63</v>
+        <v>1.28</v>
       </c>
       <c r="AE11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
         <v>1.22</v>
       </c>
-      <c r="AF11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.07</v>
-      </c>
       <c r="AK11" t="n">
-        <v>3.45</v>
+        <v>1.94</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2315,61 +2315,61 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="O12" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P12" t="n">
-        <v>3.51</v>
+        <v>2.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="R12" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="S12" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T12" t="n">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="U12" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="V12" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W12" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X12" t="n">
         <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.88</v>
+        <v>4</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AE12" t="n">
         <v>1.09</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AG12" t="n">
         <v>2.15</v>
@@ -2388,7 +2388,7 @@
         <v>1.25</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,55 +2474,55 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="O13" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P13" t="n">
-        <v>3.5</v>
+        <v>4.24</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="R13" t="n">
         <v>2.1</v>
       </c>
       <c r="S13" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T13" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="U13" t="n">
-        <v>2.77</v>
+        <v>2.94</v>
       </c>
       <c r="V13" t="n">
         <v>1.37</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X13" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.04</v>
+        <v>1.92</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.34</v>
+        <v>3.65</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE13" t="n">
         <v>1.05</v>
@@ -2531,7 +2531,7 @@
         <v>1.83</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,80 +2633,80 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="O14" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P14" t="n">
-        <v>4.19</v>
+        <v>3.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S14" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="T14" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="U14" t="n">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="V14" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X14" t="n">
         <v>1.07</v>
       </c>
-      <c r="X14" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="AD14" t="n">
         <v>1.27</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.25</v>
       </c>
       <c r="AE14" t="n">
         <v>1.05</v>
       </c>
       <c r="AF14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AK14" t="n">
         <v>1.83</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.95</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,28 +1202,28 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="O5" t="n">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="P5" t="n">
-        <v>4.6</v>
+        <v>2.88</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.31</v>
+        <v>3.12</v>
       </c>
       <c r="R5" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T5" t="n">
-        <v>2.47</v>
+        <v>2.6</v>
       </c>
       <c r="U5" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="V5" t="n">
         <v>1.28</v>
@@ -1232,34 +1232,34 @@
         <v>1.04</v>
       </c>
       <c r="X5" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.92</v>
+        <v>3.88</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.05</v>
+        <v>1.47</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,28 +1520,28 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="O7" t="n">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="P7" t="n">
-        <v>2.88</v>
+        <v>4.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.12</v>
+        <v>2.31</v>
       </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="S7" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="T7" t="n">
-        <v>2.6</v>
+        <v>2.47</v>
       </c>
       <c r="U7" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="V7" t="n">
         <v>1.28</v>
@@ -1550,34 +1550,34 @@
         <v>1.04</v>
       </c>
       <c r="X7" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.88</v>
+        <v>3.92</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.47</v>
+        <v>2.05</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,65 +1838,65 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="O9" t="n">
-        <v>5.95</v>
+        <v>5.65</v>
       </c>
       <c r="P9" t="n">
-        <v>7.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="R9" t="n">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="S9" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="T9" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U9" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="V9" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="W9" t="n">
         <v>1.17</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z9" t="n">
         <v>5.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.01</v>
+        <v>2.12</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AF9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG9" t="n">
         <v>1.83</v>
       </c>
-      <c r="AG9" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AH9" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,80 +1997,80 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="O10" t="n">
-        <v>5.65</v>
+        <v>3.48</v>
       </c>
       <c r="P10" t="n">
-        <v>8.699999999999999</v>
+        <v>4.42</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.59</v>
+        <v>2.26</v>
       </c>
       <c r="R10" t="n">
-        <v>2.73</v>
+        <v>2.25</v>
       </c>
       <c r="S10" t="n">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="T10" t="n">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="U10" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="V10" t="n">
-        <v>1.65</v>
+        <v>1.36</v>
       </c>
       <c r="W10" t="n">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.5</v>
+        <v>3.34</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.12</v>
+        <v>3.05</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.63</v>
+        <v>1.28</v>
       </c>
       <c r="AE10" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
         <v>1.22</v>
       </c>
-      <c r="AF10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AK10" t="n">
-        <v>3.75</v>
+        <v>1.94</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="O11" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="P11" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AD11" t="n">
         <v>1.7</v>
       </c>
-      <c r="O11" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="P11" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AE11" t="n">
-        <v>1.07</v>
+        <v>1.27</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.94</v>
+        <v>3.5</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,80 +2474,80 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="O13" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P13" t="n">
-        <v>4.24</v>
+        <v>3.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S13" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V13" t="n">
         <v>1.36</v>
       </c>
-      <c r="T13" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.37</v>
-      </c>
       <c r="W13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X13" t="n">
         <v>1.07</v>
       </c>
-      <c r="X13" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y13" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="AD13" t="n">
         <v>1.27</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.25</v>
       </c>
       <c r="AE13" t="n">
         <v>1.05</v>
       </c>
       <c r="AF13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AK13" t="n">
         <v>1.83</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.95</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="O14" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P14" t="n">
-        <v>3.2</v>
+        <v>4.24</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="R14" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S14" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="T14" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="U14" t="n">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="V14" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X14" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.06</v>
+        <v>1.92</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.77</v>
+        <v>3.65</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE14" t="n">
         <v>1.05</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -905,43 +905,43 @@
         <v>2.62</v>
       </c>
       <c r="U3" t="n">
-        <v>2.9</v>
+        <v>3.04</v>
       </c>
       <c r="V3" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X3" t="n">
         <v>1.06</v>
       </c>
-      <c r="X3" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Y3" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB3" t="n">
         <v>1.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.74</v>
+        <v>4.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE3" t="n">
         <v>1.03</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.58</v>
+        <v>1.33</v>
       </c>
       <c r="AK3" t="n">
         <v>1.3</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>6.5</v>
+        <v>1.67</v>
       </c>
       <c r="O4" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="P4" t="n">
-        <v>1.39</v>
+        <v>4.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>8</v>
+        <v>2.31</v>
       </c>
       <c r="R4" t="n">
-        <v>2.25</v>
+        <v>1.99</v>
       </c>
       <c r="S4" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="T4" t="n">
-        <v>2.75</v>
+        <v>2.47</v>
       </c>
       <c r="U4" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="V4" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="W4" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X4" t="n">
         <v>1.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="AA4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF4" t="n">
         <v>2.05</v>
       </c>
-      <c r="AB4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>2.21</v>
-      </c>
       <c r="AG4" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.09</v>
+        <v>2.05</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.3</v>
+        <v>6.5</v>
       </c>
       <c r="O5" t="n">
-        <v>2.96</v>
+        <v>4</v>
       </c>
       <c r="P5" t="n">
-        <v>2.88</v>
+        <v>1.39</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.12</v>
+        <v>8</v>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="S5" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="T5" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="U5" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="V5" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W5" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE5" t="n">
         <v>1.05</v>
       </c>
-      <c r="Y5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AF5" t="n">
-        <v>1.84</v>
+        <v>2.21</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.47</v>
+        <v>1.09</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.55</v>
+        <v>2.45</v>
       </c>
       <c r="O6" t="n">
-        <v>3.55</v>
+        <v>3.05</v>
       </c>
       <c r="P6" t="n">
-        <v>5.78</v>
+        <v>2.26</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="R6" t="n">
         <v>2.1</v>
       </c>
       <c r="S6" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T6" t="n">
-        <v>2.62</v>
+        <v>2.71</v>
       </c>
       <c r="U6" t="n">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="V6" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="W6" t="n">
         <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.74</v>
+        <v>3.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.15</v>
+        <v>1.58</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.61</v>
+        <v>2.12</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,25 +1520,25 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="O7" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="P7" t="n">
-        <v>4.6</v>
+        <v>5.78</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.31</v>
+        <v>2.1</v>
       </c>
       <c r="R7" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="S7" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="T7" t="n">
-        <v>2.47</v>
+        <v>2.62</v>
       </c>
       <c r="U7" t="n">
         <v>3.15</v>
@@ -1547,16 +1547,16 @@
         <v>1.28</v>
       </c>
       <c r="W7" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="AA7" t="n">
         <v>2.25</v>
@@ -1565,19 +1565,19 @@
         <v>1.62</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.92</v>
+        <v>4.2</v>
       </c>
       <c r="AD7" t="n">
         <v>1.18</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,65 +1679,65 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="O8" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="P8" t="n">
-        <v>2.26</v>
+        <v>2.88</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.5</v>
+        <v>3.12</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="T8" t="n">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="U8" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="V8" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.6</v>
+        <v>2.83</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="AB8" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG8" t="n">
         <v>1.85</v>
       </c>
-      <c r="AC8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>2.12</v>
-      </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,65 +1838,65 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="O9" t="n">
-        <v>5.65</v>
+        <v>5.95</v>
       </c>
       <c r="P9" t="n">
-        <v>8.699999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="R9" t="n">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="S9" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="T9" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U9" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="V9" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="W9" t="n">
         <v>1.17</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z9" t="n">
         <v>5.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.12</v>
+        <v>2.01</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AF9" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG9" t="n">
         <v>1.85</v>
       </c>
-      <c r="AG9" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AH9" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="O10" t="n">
-        <v>3.48</v>
+        <v>5.65</v>
       </c>
       <c r="P10" t="n">
-        <v>4.42</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.26</v>
+        <v>1.59</v>
       </c>
       <c r="R10" t="n">
-        <v>2.25</v>
+        <v>2.73</v>
       </c>
       <c r="S10" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="T10" t="n">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="U10" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="V10" t="n">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="W10" t="n">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.34</v>
+        <v>5.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.05</v>
+        <v>2.12</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.28</v>
+        <v>1.63</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.94</v>
+        <v>3.75</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.21</v>
+        <v>1.7</v>
       </c>
       <c r="O11" t="n">
-        <v>5.95</v>
+        <v>3.44</v>
       </c>
       <c r="P11" t="n">
-        <v>7.3</v>
+        <v>4.48</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.57</v>
+        <v>2.26</v>
       </c>
       <c r="R11" t="n">
-        <v>2.88</v>
+        <v>2.25</v>
       </c>
       <c r="S11" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="T11" t="n">
-        <v>3.9</v>
+        <v>2.75</v>
       </c>
       <c r="U11" t="n">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="V11" t="n">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="W11" t="n">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.5</v>
+        <v>3.34</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.44</v>
+        <v>1.85</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.62</v>
+        <v>1.85</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.01</v>
+        <v>3.05</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.7</v>
+        <v>1.33</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.27</v>
+        <v>1.07</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AK11" t="n">
-        <v>3.5</v>
+        <v>1.94</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="O13" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P13" t="n">
-        <v>3.2</v>
+        <v>4.24</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="R13" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S13" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="T13" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="U13" t="n">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="V13" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X13" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.06</v>
+        <v>1.92</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.77</v>
+        <v>3.65</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE13" t="n">
         <v>1.05</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,80 +2633,80 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="O14" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P14" t="n">
-        <v>4.24</v>
+        <v>3.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S14" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V14" t="n">
         <v>1.36</v>
       </c>
-      <c r="T14" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.37</v>
-      </c>
       <c r="W14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X14" t="n">
         <v>1.07</v>
       </c>
-      <c r="X14" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="AD14" t="n">
         <v>1.27</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.25</v>
       </c>
       <c r="AE14" t="n">
         <v>1.05</v>
       </c>
       <c r="AF14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AK14" t="n">
         <v>1.83</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.95</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.67</v>
+        <v>6.5</v>
       </c>
       <c r="O4" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="P4" t="n">
-        <v>4.6</v>
+        <v>1.39</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.31</v>
+        <v>8</v>
       </c>
       <c r="R4" t="n">
-        <v>1.99</v>
+        <v>2.25</v>
       </c>
       <c r="S4" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="T4" t="n">
-        <v>2.47</v>
+        <v>2.75</v>
       </c>
       <c r="U4" t="n">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="V4" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W4" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X4" t="n">
         <v>1.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.82</v>
+        <v>3.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.92</v>
+        <v>3.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.05</v>
+        <v>1.09</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>6.5</v>
+        <v>1.67</v>
       </c>
       <c r="O5" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="P5" t="n">
-        <v>1.39</v>
+        <v>4.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>8</v>
+        <v>2.31</v>
       </c>
       <c r="R5" t="n">
-        <v>2.25</v>
+        <v>1.99</v>
       </c>
       <c r="S5" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="T5" t="n">
-        <v>2.75</v>
+        <v>2.47</v>
       </c>
       <c r="U5" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="V5" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="W5" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X5" t="n">
         <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="AA5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF5" t="n">
         <v>2.05</v>
       </c>
-      <c r="AB5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>2.21</v>
-      </c>
       <c r="AG5" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.09</v>
+        <v>2.05</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.45</v>
+        <v>1.55</v>
       </c>
       <c r="O6" t="n">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="P6" t="n">
-        <v>2.26</v>
+        <v>5.78</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="R6" t="n">
         <v>2.1</v>
       </c>
       <c r="S6" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T6" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="U6" t="n">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="V6" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="W6" t="n">
         <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.6</v>
+        <v>2.74</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.58</v>
+        <v>2.15</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.12</v>
+        <v>1.61</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.55</v>
+        <v>2.45</v>
       </c>
       <c r="O7" t="n">
-        <v>3.55</v>
+        <v>3.05</v>
       </c>
       <c r="P7" t="n">
-        <v>5.78</v>
+        <v>2.26</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="R7" t="n">
         <v>2.1</v>
       </c>
       <c r="S7" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T7" t="n">
-        <v>2.62</v>
+        <v>2.71</v>
       </c>
       <c r="U7" t="n">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="V7" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="W7" t="n">
         <v>1.06</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.74</v>
+        <v>3.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.15</v>
+        <v>1.58</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.61</v>
+        <v>2.12</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.21</v>
+        <v>1.7</v>
       </c>
       <c r="O9" t="n">
-        <v>5.95</v>
+        <v>3.44</v>
       </c>
       <c r="P9" t="n">
-        <v>7.3</v>
+        <v>4.48</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.57</v>
+        <v>2.26</v>
       </c>
       <c r="R9" t="n">
-        <v>2.88</v>
+        <v>2.25</v>
       </c>
       <c r="S9" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="T9" t="n">
-        <v>3.9</v>
+        <v>2.75</v>
       </c>
       <c r="U9" t="n">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="V9" t="n">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="W9" t="n">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.5</v>
+        <v>3.34</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.44</v>
+        <v>1.85</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.62</v>
+        <v>1.85</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.01</v>
+        <v>3.05</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.7</v>
+        <v>1.33</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.27</v>
+        <v>1.07</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.5</v>
+        <v>1.94</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,65 +1997,65 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="O10" t="n">
-        <v>5.65</v>
+        <v>5.95</v>
       </c>
       <c r="P10" t="n">
-        <v>8.699999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="R10" t="n">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="S10" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="T10" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U10" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="V10" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="W10" t="n">
         <v>1.17</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z10" t="n">
         <v>5.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.12</v>
+        <v>2.01</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AF10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG10" t="n">
         <v>1.85</v>
       </c>
-      <c r="AG10" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AH10" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="O11" t="n">
-        <v>3.44</v>
+        <v>5.65</v>
       </c>
       <c r="P11" t="n">
-        <v>4.48</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.26</v>
+        <v>1.59</v>
       </c>
       <c r="R11" t="n">
-        <v>2.25</v>
+        <v>2.73</v>
       </c>
       <c r="S11" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="T11" t="n">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="U11" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="V11" t="n">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="W11" t="n">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.34</v>
+        <v>5.5</v>
       </c>
       <c r="AA11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF11" t="n">
         <v>1.85</v>
       </c>
-      <c r="AB11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AG11" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.94</v>
+        <v>3.75</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,61 +2474,61 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.83</v>
+        <v>2.12</v>
       </c>
       <c r="O13" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P13" t="n">
-        <v>4.24</v>
+        <v>3.51</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="V13" t="n">
         <v>1.36</v>
       </c>
-      <c r="T13" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.37</v>
-      </c>
       <c r="W13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X13" t="n">
         <v>1.07</v>
       </c>
-      <c r="X13" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y13" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.65</v>
+        <v>3.79</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE13" t="n">
         <v>1.05</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG13" t="n">
         <v>1.87</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="O14" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P14" t="n">
-        <v>3.2</v>
+        <v>4.24</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="R14" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S14" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="T14" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="U14" t="n">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="V14" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X14" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.06</v>
+        <v>1.92</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.77</v>
+        <v>3.65</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE14" t="n">
         <v>1.05</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="O2" t="n">
-        <v>3.46</v>
+        <v>3.21</v>
       </c>
       <c r="P2" t="n">
         <v>2.85</v>
@@ -737,13 +737,13 @@
         <v>2.45</v>
       </c>
       <c r="R2" t="n">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="S2" t="n">
         <v>1.29</v>
       </c>
       <c r="T2" t="n">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="U2" t="n">
         <v>2.4</v>
@@ -755,34 +755,34 @@
         <v>1.08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.6</v>
+        <v>3.98</v>
       </c>
       <c r="AA2" t="n">
         <v>1.7</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AC2" t="n">
         <v>2.75</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE2" t="n">
         <v>1.13</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>6.5</v>
+        <v>2.45</v>
       </c>
       <c r="O4" t="n">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="P4" t="n">
-        <v>1.39</v>
+        <v>2.26</v>
       </c>
       <c r="Q4" t="n">
-        <v>8</v>
+        <v>3.5</v>
       </c>
       <c r="R4" t="n">
-        <v>2.25</v>
+        <v>2.01</v>
       </c>
       <c r="S4" t="n">
         <v>1.36</v>
       </c>
       <c r="T4" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U4" t="n">
         <v>2.75</v>
       </c>
-      <c r="U4" t="n">
-        <v>2.8</v>
-      </c>
       <c r="V4" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W4" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X4" t="n">
         <v>1.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z4" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC4" t="n">
         <v>3.2</v>
       </c>
-      <c r="AA4" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>3.6</v>
-      </c>
       <c r="AD4" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.21</v>
+        <v>1.7</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.58</v>
+        <v>2</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.09</v>
+        <v>1.4</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.55</v>
+        <v>6.5</v>
       </c>
       <c r="O6" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="P6" t="n">
-        <v>5.78</v>
+        <v>1.39</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.1</v>
+        <v>8</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S6" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T6" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="U6" t="n">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="V6" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W6" t="n">
         <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.74</v>
+        <v>3.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.2</v>
+        <v>1.09</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.45</v>
+        <v>1.55</v>
       </c>
       <c r="O7" t="n">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="P7" t="n">
-        <v>2.26</v>
+        <v>5.78</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="R7" t="n">
         <v>2.1</v>
       </c>
       <c r="S7" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T7" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="U7" t="n">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="V7" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="W7" t="n">
         <v>1.06</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.6</v>
+        <v>2.74</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.58</v>
+        <v>2.15</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.12</v>
+        <v>1.61</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,61 +1838,61 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.7</v>
+        <v>1.21</v>
       </c>
       <c r="O9" t="n">
-        <v>3.44</v>
+        <v>4.75</v>
       </c>
       <c r="P9" t="n">
-        <v>4.48</v>
+        <v>7.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.26</v>
+        <v>1.66</v>
       </c>
       <c r="R9" t="n">
-        <v>2.25</v>
+        <v>2.69</v>
       </c>
       <c r="S9" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="T9" t="n">
-        <v>2.75</v>
+        <v>4.2</v>
       </c>
       <c r="U9" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="V9" t="n">
-        <v>1.36</v>
+        <v>1.64</v>
       </c>
       <c r="W9" t="n">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="X9" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE9" t="n">
         <v>1.24</v>
       </c>
-      <c r="Z9" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.07</v>
-      </c>
       <c r="AF9" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="AG9" t="n">
         <v>1.9</v>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.94</v>
+        <v>3.4</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,19 +1997,19 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="O10" t="n">
-        <v>5.95</v>
+        <v>6.5</v>
       </c>
       <c r="P10" t="n">
-        <v>7.3</v>
+        <v>9.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="R10" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="S10" t="n">
         <v>1.21</v>
@@ -2018,43 +2018,43 @@
         <v>3.9</v>
       </c>
       <c r="U10" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="V10" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="W10" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AE10" t="n">
         <v>1.27</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,80 +2156,80 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="O11" t="n">
-        <v>5.65</v>
+        <v>3.44</v>
       </c>
       <c r="P11" t="n">
-        <v>8.699999999999999</v>
+        <v>4.48</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.59</v>
+        <v>2.26</v>
       </c>
       <c r="R11" t="n">
-        <v>2.73</v>
+        <v>2.25</v>
       </c>
       <c r="S11" t="n">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="T11" t="n">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="U11" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="V11" t="n">
-        <v>1.65</v>
+        <v>1.36</v>
       </c>
       <c r="W11" t="n">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.5</v>
+        <v>3.34</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.12</v>
+        <v>3.05</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.63</v>
+        <v>1.33</v>
       </c>
       <c r="AE11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
         <v>1.22</v>
       </c>
-      <c r="AF11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AK11" t="n">
-        <v>3.75</v>
+        <v>1.94</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2324,10 +2324,10 @@
         <v>2.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.55</v>
+        <v>2.49</v>
       </c>
       <c r="R12" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="S12" t="n">
         <v>1.3</v>
@@ -2336,34 +2336,34 @@
         <v>3.04</v>
       </c>
       <c r="U12" t="n">
-        <v>2.56</v>
+        <v>2.28</v>
       </c>
       <c r="V12" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W12" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X12" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z12" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AA12" t="n">
         <v>1.73</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AE12" t="n">
         <v>1.09</v>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,61 +2474,61 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.12</v>
+        <v>1.83</v>
       </c>
       <c r="O13" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P13" t="n">
-        <v>3.51</v>
+        <v>4.24</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="R13" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S13" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="T13" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="U13" t="n">
-        <v>2.82</v>
+        <v>2.94</v>
       </c>
       <c r="V13" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X13" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.79</v>
+        <v>3.65</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE13" t="n">
         <v>1.05</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG13" t="n">
         <v>1.87</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,61 +2633,61 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.83</v>
+        <v>2.12</v>
       </c>
       <c r="O14" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P14" t="n">
-        <v>4.24</v>
+        <v>3.51</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="V14" t="n">
         <v>1.36</v>
       </c>
-      <c r="T14" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.37</v>
-      </c>
       <c r="W14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X14" t="n">
         <v>1.07</v>
       </c>
-      <c r="X14" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y14" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE14" t="n">
         <v>1.05</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG14" t="n">
         <v>1.87</v>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -884,25 +884,25 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3.21</v>
+        <v>2.71</v>
       </c>
       <c r="O3" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="P3" t="n">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="R3" t="n">
         <v>1.97</v>
       </c>
       <c r="S3" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T3" t="n">
-        <v>2.62</v>
+        <v>2.47</v>
       </c>
       <c r="U3" t="n">
         <v>3.04</v>
@@ -914,34 +914,34 @@
         <v>1.04</v>
       </c>
       <c r="X3" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.2</v>
+        <v>3.74</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE3" t="n">
         <v>1.03</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,80 +1043,80 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.45</v>
+        <v>7.9</v>
       </c>
       <c r="O4" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z4" t="n">
         <v>3.05</v>
       </c>
-      <c r="P4" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X4" t="n">
+      <c r="AA4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AK4" t="n">
         <v>1.03</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.4</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.67</v>
+        <v>2.45</v>
       </c>
       <c r="O5" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="P5" t="n">
-        <v>4.6</v>
+        <v>2.26</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.31</v>
+        <v>3.5</v>
       </c>
       <c r="R5" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="S5" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="T5" t="n">
-        <v>2.47</v>
+        <v>2.73</v>
       </c>
       <c r="U5" t="n">
-        <v>3.15</v>
+        <v>2.75</v>
       </c>
       <c r="V5" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="W5" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X5" t="n">
         <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.82</v>
+        <v>3.14</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.92</v>
+        <v>3.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.05</v>
+        <v>1.4</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>6.5</v>
+        <v>2.3</v>
       </c>
       <c r="O6" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="P6" t="n">
-        <v>1.39</v>
+        <v>2.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>8</v>
+        <v>2.88</v>
       </c>
       <c r="R6" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="T6" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="U6" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="V6" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y6" t="n">
         <v>1.33</v>
       </c>
-      <c r="W6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.3</v>
-      </c>
       <c r="Z6" t="n">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.6</v>
+        <v>3.86</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.21</v>
+        <v>1.83</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.58</v>
+        <v>1.86</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.09</v>
+        <v>1.45</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1520,43 +1520,43 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="O7" t="n">
-        <v>3.55</v>
+        <v>3.64</v>
       </c>
       <c r="P7" t="n">
-        <v>5.78</v>
+        <v>6.14</v>
       </c>
       <c r="Q7" t="n">
         <v>2.1</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="S7" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T7" t="n">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="U7" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="V7" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W7" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X7" t="n">
         <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="AA7" t="n">
         <v>2.25</v>
@@ -1565,19 +1565,19 @@
         <v>1.62</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AD7" t="n">
         <v>1.18</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,28 +1679,28 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="O8" t="n">
-        <v>2.96</v>
+        <v>3.3</v>
       </c>
       <c r="P8" t="n">
-        <v>2.88</v>
+        <v>4.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.12</v>
+        <v>2.24</v>
       </c>
       <c r="R8" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="S8" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="T8" t="n">
-        <v>2.6</v>
+        <v>2.47</v>
       </c>
       <c r="U8" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="V8" t="n">
         <v>1.28</v>
@@ -1709,34 +1709,34 @@
         <v>1.04</v>
       </c>
       <c r="X8" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE8" t="n">
         <v>1.02</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.84</v>
+        <v>2.07</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.47</v>
+        <v>2.06</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,61 +1838,61 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.21</v>
+        <v>1.7</v>
       </c>
       <c r="O9" t="n">
-        <v>4.75</v>
+        <v>3.5</v>
       </c>
       <c r="P9" t="n">
-        <v>7.3</v>
+        <v>4.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.66</v>
+        <v>2.26</v>
       </c>
       <c r="R9" t="n">
-        <v>2.69</v>
+        <v>2.08</v>
       </c>
       <c r="S9" t="n">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="T9" t="n">
-        <v>4.2</v>
+        <v>2.75</v>
       </c>
       <c r="U9" t="n">
-        <v>2.1</v>
+        <v>2.71</v>
       </c>
       <c r="V9" t="n">
-        <v>1.64</v>
+        <v>1.37</v>
       </c>
       <c r="W9" t="n">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.5</v>
+        <v>3.34</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.44</v>
+        <v>1.9</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.62</v>
+        <v>1.9</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.08</v>
+        <v>3.05</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AG9" t="n">
         <v>1.9</v>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.4</v>
+        <v>2.06</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,80 +1997,80 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="O10" t="n">
-        <v>6.5</v>
+        <v>4.75</v>
       </c>
       <c r="P10" t="n">
-        <v>9.5</v>
+        <v>7.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="R10" t="n">
-        <v>3.1</v>
+        <v>2.69</v>
       </c>
       <c r="S10" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="T10" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="U10" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="V10" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="W10" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
         <v>1.01</v>
       </c>
-      <c r="Y10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AK10" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.7</v>
+        <v>1.15</v>
       </c>
       <c r="O11" t="n">
-        <v>3.44</v>
+        <v>6.5</v>
       </c>
       <c r="P11" t="n">
-        <v>4.48</v>
+        <v>9.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.26</v>
+        <v>1.5</v>
       </c>
       <c r="R11" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="S11" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="T11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB11" t="n">
         <v>2.75</v>
       </c>
-      <c r="U11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AA11" t="n">
+      <c r="AC11" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF11" t="n">
         <v>1.85</v>
       </c>
-      <c r="AB11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AG11" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.94</v>
+        <v>3.5</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2480,13 +2480,13 @@
         <v>3.3</v>
       </c>
       <c r="P13" t="n">
-        <v>4.24</v>
+        <v>4.29</v>
       </c>
       <c r="Q13" t="n">
         <v>2.45</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S13" t="n">
         <v>1.36</v>
@@ -2495,13 +2495,13 @@
         <v>2.9</v>
       </c>
       <c r="U13" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="V13" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W13" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X13" t="n">
         <v>1.01</v>
@@ -2516,22 +2516,22 @@
         <v>1.92</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.65</v>
+        <v>3.28</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE13" t="n">
         <v>1.05</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7.9</v>
+        <v>2.3</v>
       </c>
       <c r="O4" t="n">
-        <v>3.94</v>
+        <v>2.9</v>
       </c>
       <c r="P4" t="n">
-        <v>1.37</v>
+        <v>2.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.42</v>
+        <v>2.88</v>
       </c>
       <c r="R4" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="S4" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="T4" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="U4" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="V4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y4" t="n">
         <v>1.33</v>
       </c>
-      <c r="W4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.28</v>
-      </c>
       <c r="Z4" t="n">
-        <v>3.05</v>
+        <v>2.83</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.6</v>
+        <v>3.86</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.19</v>
+        <v>1.83</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.59</v>
+        <v>1.86</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.03</v>
+        <v>1.45</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.45</v>
+        <v>1.67</v>
       </c>
       <c r="O5" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="P5" t="n">
-        <v>2.26</v>
+        <v>4.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.5</v>
+        <v>2.24</v>
       </c>
       <c r="R5" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="S5" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="T5" t="n">
-        <v>2.73</v>
+        <v>2.47</v>
       </c>
       <c r="U5" t="n">
-        <v>2.75</v>
+        <v>3.15</v>
       </c>
       <c r="V5" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="W5" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X5" t="n">
         <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.27</v>
+        <v>1.39</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.14</v>
+        <v>2.82</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.7</v>
+        <v>2.07</v>
       </c>
       <c r="AG5" t="n">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.4</v>
+        <v>2.06</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.3</v>
+        <v>7.9</v>
       </c>
       <c r="O6" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U6" t="n">
         <v>2.9</v>
       </c>
-      <c r="P6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3.3</v>
-      </c>
       <c r="V6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y6" t="n">
         <v>1.28</v>
       </c>
-      <c r="W6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X6" t="n">
+      <c r="Z6" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE6" t="n">
         <v>1.05</v>
       </c>
-      <c r="Y6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AF6" t="n">
-        <v>1.83</v>
+        <v>2.19</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.86</v>
+        <v>1.59</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.45</v>
+        <v>1.03</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,80 +1520,80 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.51</v>
+        <v>2.45</v>
       </c>
       <c r="O7" t="n">
-        <v>3.64</v>
+        <v>3.05</v>
       </c>
       <c r="P7" t="n">
-        <v>6.14</v>
+        <v>2.26</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="R7" t="n">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="S7" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="T7" t="n">
-        <v>2.57</v>
+        <v>2.73</v>
       </c>
       <c r="U7" t="n">
-        <v>3.12</v>
+        <v>2.75</v>
       </c>
       <c r="V7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
         <v>1.29</v>
       </c>
-      <c r="W7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AK7" t="n">
-        <v>2.16</v>
+        <v>1.4</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,43 +1679,43 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.67</v>
+        <v>1.51</v>
       </c>
       <c r="O8" t="n">
-        <v>3.3</v>
+        <v>3.64</v>
       </c>
       <c r="P8" t="n">
-        <v>4.6</v>
+        <v>6.14</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="R8" t="n">
-        <v>1.99</v>
+        <v>2.07</v>
       </c>
       <c r="S8" t="n">
         <v>1.45</v>
       </c>
       <c r="T8" t="n">
-        <v>2.47</v>
+        <v>2.57</v>
       </c>
       <c r="U8" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="V8" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W8" t="n">
         <v>1.04</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="AA8" t="n">
         <v>2.25</v>
@@ -1724,19 +1724,19 @@
         <v>1.62</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AD8" t="n">
         <v>1.18</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>1.2</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="O10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="P10" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S10" t="n">
         <v>1.21</v>
       </c>
-      <c r="O10" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="P10" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.19</v>
-      </c>
       <c r="T10" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="U10" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="V10" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="W10" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,80 +2156,80 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="O11" t="n">
-        <v>6.5</v>
+        <v>4.75</v>
       </c>
       <c r="P11" t="n">
-        <v>9.5</v>
+        <v>7.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="R11" t="n">
-        <v>3.1</v>
+        <v>2.69</v>
       </c>
       <c r="S11" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="T11" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="U11" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="V11" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="W11" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
         <v>1.01</v>
       </c>
-      <c r="Y11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AK11" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2477,25 +2477,25 @@
         <v>1.83</v>
       </c>
       <c r="O13" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P13" t="n">
-        <v>4.29</v>
+        <v>3.8</v>
       </c>
       <c r="Q13" t="n">
         <v>2.45</v>
       </c>
       <c r="R13" t="n">
-        <v>2.05</v>
+        <v>2.24</v>
       </c>
       <c r="S13" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T13" t="n">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="U13" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="V13" t="n">
         <v>1.38</v>
@@ -2507,31 +2507,31 @@
         <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,65 +1043,65 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.3</v>
+        <v>7.5</v>
       </c>
       <c r="O4" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="P4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="U4" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U4" t="n">
-        <v>3.3</v>
-      </c>
       <c r="V4" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W4" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X4" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AB4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG4" t="n">
         <v>1.62</v>
       </c>
-      <c r="AC4" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.86</v>
-      </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.45</v>
+        <v>1.08</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.67</v>
+        <v>2.14</v>
       </c>
       <c r="O5" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="P5" t="n">
-        <v>4.6</v>
+        <v>2.88</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.24</v>
+        <v>2.63</v>
       </c>
       <c r="R5" t="n">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="S5" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T5" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="U5" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="V5" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W5" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X5" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.9</v>
+        <v>3.74</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE5" t="n">
         <v>1.02</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.07</v>
+        <v>1.8</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.06</v>
+        <v>1.57</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>7.9</v>
+        <v>1.67</v>
       </c>
       <c r="O6" t="n">
-        <v>3.94</v>
+        <v>3.25</v>
       </c>
       <c r="P6" t="n">
-        <v>1.37</v>
+        <v>4.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.42</v>
+        <v>2.25</v>
       </c>
       <c r="R6" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="S6" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y6" t="n">
         <v>1.4</v>
       </c>
-      <c r="T6" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.28</v>
-      </c>
       <c r="Z6" t="n">
-        <v>3.05</v>
+        <v>2.63</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.6</v>
+        <v>3.98</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AE6" t="n">
         <v>1.05</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.03</v>
+        <v>2</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.45</v>
+        <v>1.48</v>
       </c>
       <c r="O7" t="n">
-        <v>3.05</v>
+        <v>3.75</v>
       </c>
       <c r="P7" t="n">
-        <v>2.26</v>
+        <v>6</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="R7" t="n">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="S7" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y7" t="n">
         <v>1.36</v>
       </c>
-      <c r="T7" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.27</v>
-      </c>
       <c r="Z7" t="n">
-        <v>3.14</v>
+        <v>2.87</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AG7" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,80 +1679,80 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.51</v>
+        <v>2.45</v>
       </c>
       <c r="O8" t="n">
-        <v>3.64</v>
+        <v>3.05</v>
       </c>
       <c r="P8" t="n">
-        <v>6.14</v>
+        <v>2.26</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="R8" t="n">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="S8" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="T8" t="n">
-        <v>2.57</v>
+        <v>2.73</v>
       </c>
       <c r="U8" t="n">
-        <v>3.12</v>
+        <v>2.75</v>
       </c>
       <c r="V8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
         <v>1.29</v>
       </c>
-      <c r="W8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AK8" t="n">
-        <v>2.16</v>
+        <v>1.4</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,80 +1838,80 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.7</v>
+        <v>1.15</v>
       </c>
       <c r="O9" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="P9" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK9" t="n">
         <v>3.5</v>
-      </c>
-      <c r="P9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>2.06</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,80 +1997,80 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="O10" t="n">
-        <v>6.5</v>
+        <v>4.75</v>
       </c>
       <c r="P10" t="n">
-        <v>9.5</v>
+        <v>7.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="R10" t="n">
-        <v>3.1</v>
+        <v>2.69</v>
       </c>
       <c r="S10" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="T10" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="U10" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="V10" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="W10" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
         <v>1.01</v>
       </c>
-      <c r="Y10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AK10" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,61 +2156,61 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.21</v>
+        <v>1.7</v>
       </c>
       <c r="O11" t="n">
-        <v>4.75</v>
+        <v>3.5</v>
       </c>
       <c r="P11" t="n">
-        <v>7.3</v>
+        <v>4.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.66</v>
+        <v>2.26</v>
       </c>
       <c r="R11" t="n">
-        <v>2.69</v>
+        <v>2.08</v>
       </c>
       <c r="S11" t="n">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="T11" t="n">
-        <v>4.2</v>
+        <v>2.75</v>
       </c>
       <c r="U11" t="n">
-        <v>2.1</v>
+        <v>2.71</v>
       </c>
       <c r="V11" t="n">
-        <v>1.64</v>
+        <v>1.37</v>
       </c>
       <c r="W11" t="n">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.5</v>
+        <v>3.34</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.44</v>
+        <v>1.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.62</v>
+        <v>1.9</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.08</v>
+        <v>3.05</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AG11" t="n">
         <v>1.9</v>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AK11" t="n">
-        <v>3.4</v>
+        <v>2.06</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -702,13 +702,13 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -717,11 +717,11 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2" t="n">
@@ -737,95 +737,95 @@
         <v>2.45</v>
       </c>
       <c r="R2" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="S2" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T2" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U2" t="n">
         <v>2.4</v>
       </c>
       <c r="V2" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W2" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X2" t="n">
         <v>1.03</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z2" t="n">
         <v>3.98</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AB2" t="n">
         <v>2.1</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.75</v>
+        <v>2.52</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['28']</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['71', '88']</t>
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN2" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO2" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AP2" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>0.66</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AU2" s="3" t="n">
         <v>46191.41666666666</v>
@@ -861,10 +861,10 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -873,118 +873,118 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.71</v>
+        <v>3.15</v>
       </c>
       <c r="O3" t="n">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="P3" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.58</v>
+        <v>3.75</v>
       </c>
       <c r="R3" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="S3" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T3" t="n">
-        <v>2.47</v>
+        <v>2.41</v>
       </c>
       <c r="U3" t="n">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W3" t="n">
         <v>1.04</v>
       </c>
       <c r="X3" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.74</v>
+        <v>4</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AE3" t="n">
         <v>1.03</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['61']</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['51']</t>
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN3" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO3" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP3" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AU3" s="3" t="n">
         <v>46191.4375</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,31 +1043,31 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7.5</v>
+        <v>2.14</v>
       </c>
       <c r="O4" t="n">
-        <v>3.9</v>
+        <v>3.05</v>
       </c>
       <c r="P4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S4" t="n">
         <v>1.44</v>
       </c>
-      <c r="Q4" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.41</v>
-      </c>
       <c r="T4" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="U4" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="V4" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W4" t="n">
         <v>1.05</v>
@@ -1076,31 +1076,31 @@
         <v>1.06</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z4" t="n">
         <v>3</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.6</v>
+        <v>3.74</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.08</v>
+        <v>1.57</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.14</v>
+        <v>1.48</v>
       </c>
       <c r="O5" t="n">
-        <v>3.05</v>
+        <v>3.75</v>
       </c>
       <c r="P5" t="n">
-        <v>2.88</v>
+        <v>6</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="R5" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S5" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="T5" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="U5" t="n">
-        <v>3.2</v>
+        <v>2.91</v>
       </c>
       <c r="V5" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="W5" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE5" t="n">
         <v>1.06</v>
       </c>
-      <c r="Y5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AF5" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.57</v>
+        <v>2.3</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.67</v>
+        <v>7.5</v>
       </c>
       <c r="O6" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="P6" t="n">
-        <v>4.6</v>
+        <v>1.44</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.25</v>
+        <v>6.5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="S6" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="T6" t="n">
-        <v>2.44</v>
+        <v>2.59</v>
       </c>
       <c r="U6" t="n">
-        <v>3.18</v>
+        <v>2.8</v>
       </c>
       <c r="V6" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W6" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE6" t="n">
         <v>1.08</v>
       </c>
-      <c r="Y6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AF6" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AK6" t="n">
-        <v>2</v>
+        <v>1.08</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,32 +1478,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1516,111 +1516,111 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.48</v>
+        <v>2.45</v>
       </c>
       <c r="O7" t="n">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="P7" t="n">
-        <v>6</v>
+        <v>2.37</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S7" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="T7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U7" t="n">
         <v>2.48</v>
       </c>
-      <c r="U7" t="n">
-        <v>2.91</v>
-      </c>
       <c r="V7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD7" t="n">
         <v>1.34</v>
       </c>
-      <c r="W7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC7" t="n">
+      <c r="AE7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>['5', '28']</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
         <v>4</v>
       </c>
-      <c r="AD7" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>-1</v>
-      </c>
       <c r="AN7" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO7" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP7" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AU7" s="3" t="n">
         <v>46191.45833333334</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,80 +1679,80 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.45</v>
+        <v>1.67</v>
       </c>
       <c r="O8" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="P8" t="n">
-        <v>2.26</v>
+        <v>4.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.5</v>
+        <v>2.25</v>
       </c>
       <c r="R8" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="S8" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="T8" t="n">
-        <v>2.73</v>
+        <v>2.44</v>
       </c>
       <c r="U8" t="n">
-        <v>2.75</v>
+        <v>3.18</v>
       </c>
       <c r="V8" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="W8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X8" t="n">
         <v>1.08</v>
       </c>
-      <c r="X8" t="n">
-        <v>1.03</v>
-      </c>
       <c r="Y8" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.14</v>
+        <v>2.63</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.2</v>
+        <v>3.98</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AG8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AK8" t="n">
         <v>2</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.4</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="O9" t="n">
-        <v>6.5</v>
+        <v>4.6</v>
       </c>
       <c r="P9" t="n">
-        <v>9.5</v>
+        <v>5.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="R9" t="n">
-        <v>3.1</v>
+        <v>2.67</v>
       </c>
       <c r="S9" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T9" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U9" t="n">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="V9" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="W9" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z9" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.02</v>
+        <v>2.23</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,80 +1997,80 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.21</v>
+        <v>1.7</v>
       </c>
       <c r="O10" t="n">
-        <v>4.75</v>
+        <v>3.4</v>
       </c>
       <c r="P10" t="n">
-        <v>7.3</v>
+        <v>4.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.66</v>
+        <v>2.2</v>
       </c>
       <c r="R10" t="n">
-        <v>2.69</v>
+        <v>2.25</v>
       </c>
       <c r="S10" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="T10" t="n">
-        <v>4.2</v>
+        <v>2.75</v>
       </c>
       <c r="U10" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK10" t="n">
         <v>2.1</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>3.4</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.7</v>
+        <v>1.22</v>
       </c>
       <c r="O11" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="P11" t="n">
-        <v>4.2</v>
+        <v>8</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.26</v>
+        <v>1.57</v>
       </c>
       <c r="R11" t="n">
-        <v>2.08</v>
+        <v>2.78</v>
       </c>
       <c r="S11" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="T11" t="n">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
       <c r="U11" t="n">
-        <v>2.71</v>
+        <v>2.05</v>
       </c>
       <c r="V11" t="n">
-        <v>1.37</v>
+        <v>1.73</v>
       </c>
       <c r="W11" t="n">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.34</v>
+        <v>5.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.9</v>
+        <v>1.44</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.9</v>
+        <v>2.62</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.05</v>
+        <v>1.93</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.06</v>
+        <v>2.85</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2315,58 +2315,58 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="O12" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P12" t="n">
         <v>2.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.49</v>
+        <v>2.42</v>
       </c>
       <c r="R12" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="S12" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T12" t="n">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="U12" t="n">
         <v>2.28</v>
       </c>
       <c r="V12" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W12" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AA12" t="n">
         <v>1.73</v>
       </c>
       <c r="AB12" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC12" t="n">
         <v>2.75</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF12" t="n">
         <v>1.62</v>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.83</v>
+        <v>2.12</v>
       </c>
       <c r="O13" t="n">
-        <v>3.25</v>
+        <v>3.16</v>
       </c>
       <c r="P13" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="R13" t="n">
-        <v>2.24</v>
+        <v>2.19</v>
       </c>
       <c r="S13" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T13" t="n">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="U13" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="V13" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W13" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="AD13" t="n">
         <v>1.28</v>
       </c>
-      <c r="Z13" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AE13" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.12</v>
+        <v>1.83</v>
       </c>
       <c r="O14" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P14" t="n">
-        <v>3.51</v>
+        <v>3.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="R14" t="n">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="S14" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T14" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="U14" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="V14" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X14" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -1011,63 +1011,63 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.14</v>
+        <v>7.5</v>
       </c>
       <c r="O4" t="n">
-        <v>3.05</v>
+        <v>3.9</v>
       </c>
       <c r="P4" t="n">
-        <v>2.88</v>
+        <v>1.44</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.63</v>
+        <v>6.5</v>
       </c>
       <c r="R4" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="S4" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="T4" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="U4" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="V4" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W4" t="n">
         <v>1.05</v>
@@ -1076,74 +1076,74 @@
         <v>1.06</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z4" t="n">
         <v>3</v>
       </c>
       <c r="AA4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF4" t="n">
         <v>2.15</v>
       </c>
-      <c r="AB4" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AG4" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['88']</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['7']</t>
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.57</v>
+        <v>1.08</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN4" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO4" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP4" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AU4" s="3" t="n">
         <v>46191.45833333334</v>
@@ -1160,32 +1160,32 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -1198,111 +1198,111 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.48</v>
+        <v>2.45</v>
       </c>
       <c r="O5" t="n">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="P5" t="n">
-        <v>6</v>
+        <v>2.37</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S5" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="T5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U5" t="n">
         <v>2.48</v>
       </c>
-      <c r="U5" t="n">
-        <v>2.91</v>
-      </c>
       <c r="V5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD5" t="n">
         <v>1.34</v>
       </c>
-      <c r="W5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC5" t="n">
+      <c r="AE5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>['5', '28']</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
         <v>4</v>
       </c>
-      <c r="AD5" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>-1</v>
-      </c>
       <c r="AN5" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO5" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP5" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AU5" s="3" t="n">
         <v>46191.45833333334</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1357,65 +1357,65 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>7.5</v>
+        <v>1.48</v>
       </c>
       <c r="O6" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="P6" t="n">
-        <v>1.44</v>
+        <v>6</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.5</v>
+        <v>2.1</v>
       </c>
       <c r="R6" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S6" t="n">
         <v>1.41</v>
       </c>
       <c r="T6" t="n">
-        <v>2.59</v>
+        <v>2.48</v>
       </c>
       <c r="U6" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="V6" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W6" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE6" t="n">
         <v>1.06</v>
       </c>
-      <c r="Y6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AF6" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG6" t="n">
         <v>1.62</v>
@@ -1431,37 +1431,37 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.08</v>
+        <v>2.3</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN6" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO6" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP6" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>0.66</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AU6" s="3" t="n">
         <v>46191.45833333334</v>
@@ -1478,41 +1478,41 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>2</v>
       </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1520,80 +1520,80 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.45</v>
+        <v>2.14</v>
       </c>
       <c r="O7" t="n">
         <v>3.05</v>
       </c>
       <c r="P7" t="n">
-        <v>2.37</v>
+        <v>2.88</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="R7" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="S7" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="T7" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="U7" t="n">
-        <v>2.48</v>
+        <v>3.2</v>
       </c>
       <c r="V7" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="W7" t="n">
         <v>1.05</v>
       </c>
       <c r="X7" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="AB7" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF7" t="n">
         <v>1.8</v>
       </c>
-      <c r="AC7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AG7" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>['5', '28']</t>
+          <t>['89', '90+5']</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['53']</t>
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1605,22 +1605,22 @@
         <v>2</v>
       </c>
       <c r="AO7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP7" t="n">
         <v>7</v>
       </c>
-      <c r="AP7" t="n">
-        <v>5</v>
-      </c>
       <c r="AQ7" t="n">
-        <v>1.07</v>
+        <v>1.34</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="AS7" t="n">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="AT7" t="n">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="AU7" s="3" t="n">
         <v>46191.45833333334</v>
@@ -1656,26 +1656,26 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8" t="n">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['50']</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+2', '61']</t>
         </is>
       </c>
       <c r="AJ8" t="n">
@@ -1758,28 +1758,28 @@
         <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN8" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO8" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP8" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AU8" s="3" t="n">
         <v>46191.45833333334</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,139 +1806,139 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.28</v>
+        <v>1.7</v>
       </c>
       <c r="O9" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="P9" t="n">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="R9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U9" t="n">
         <v>2.67</v>
       </c>
-      <c r="S9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="T9" t="n">
+      <c r="V9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>['12', '15', '49', '66', '79']</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>['1', '37', '90+1']</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AN9" t="n">
         <v>4</v>
       </c>
-      <c r="U9" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>-1</v>
-      </c>
       <c r="AO9" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP9" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AU9" s="3" t="n">
         <v>46191.54166666666</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,139 +1965,139 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="O10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="Q10" t="n">
         <v>1.7</v>
       </c>
-      <c r="O10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG10" t="n">
         <v>2.2</v>
       </c>
-      <c r="R10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X10" t="n">
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>['5', '24', '88']</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>['37', '60']</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AN10" t="n">
         <v>1</v>
       </c>
-      <c r="Y10" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>-1</v>
-      </c>
       <c r="AO10" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP10" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>0.41</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AU10" s="3" t="n">
         <v>46191.54166666666</v>
@@ -2133,26 +2133,26 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['7', '78']</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -2235,28 +2235,28 @@
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN11" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO11" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP11" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AU11" s="3" t="n">
         <v>46191.54166666666</v>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -2394,28 +2394,28 @@
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN12" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO12" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP12" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AU12" s="3" t="n">
         <v>46191.58333333334</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.12</v>
+        <v>1.84</v>
       </c>
       <c r="O13" t="n">
-        <v>3.16</v>
+        <v>3.3</v>
       </c>
       <c r="P13" t="n">
-        <v>3.35</v>
+        <v>3.58</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="R13" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="S13" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="T13" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="U13" t="n">
-        <v>2.82</v>
+        <v>2.98</v>
       </c>
       <c r="V13" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.77</v>
+        <v>3.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.67</v>
+        <v>1.92</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.83</v>
+        <v>2.12</v>
       </c>
       <c r="O14" t="n">
-        <v>3.25</v>
+        <v>3.16</v>
       </c>
       <c r="P14" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="R14" t="n">
-        <v>2.24</v>
+        <v>2.19</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T14" t="n">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="U14" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="V14" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W14" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="AD14" t="n">
         <v>1.28</v>
       </c>
-      <c r="Z14" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AE14" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -1011,28 +1011,28 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1043,80 +1043,80 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7.5</v>
+        <v>1.48</v>
       </c>
       <c r="O4" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="P4" t="n">
-        <v>1.44</v>
+        <v>6</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.5</v>
+        <v>2.1</v>
       </c>
       <c r="R4" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S4" t="n">
         <v>1.41</v>
       </c>
       <c r="T4" t="n">
-        <v>2.59</v>
+        <v>2.48</v>
       </c>
       <c r="U4" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="V4" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W4" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE4" t="n">
         <v>1.06</v>
       </c>
-      <c r="Y4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AF4" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG4" t="n">
         <v>1.62</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>['88']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>['7']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.08</v>
+        <v>2.3</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1131,19 +1131,19 @@
         <v>9</v>
       </c>
       <c r="AP4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.09</v>
+        <v>1.24</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.04</v>
+        <v>0.66</v>
       </c>
       <c r="AS4" t="n">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="AT4" t="n">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="AU4" s="3" t="n">
         <v>46191.45833333334</v>
@@ -1160,41 +1160,41 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
         <v>2</v>
       </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1202,80 +1202,80 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.45</v>
+        <v>2.14</v>
       </c>
       <c r="O5" t="n">
         <v>3.05</v>
       </c>
       <c r="P5" t="n">
-        <v>2.37</v>
+        <v>2.88</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="R5" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="S5" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="T5" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="U5" t="n">
-        <v>2.48</v>
+        <v>3.2</v>
       </c>
       <c r="V5" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="W5" t="n">
         <v>1.05</v>
       </c>
       <c r="X5" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="AB5" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF5" t="n">
         <v>1.8</v>
       </c>
-      <c r="AC5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AG5" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>['5', '28']</t>
+          <t>['89', '90+5']</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['53']</t>
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1287,22 +1287,22 @@
         <v>2</v>
       </c>
       <c r="AO5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP5" t="n">
         <v>7</v>
       </c>
-      <c r="AP5" t="n">
-        <v>5</v>
-      </c>
       <c r="AQ5" t="n">
-        <v>1.07</v>
+        <v>1.34</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="AS5" t="n">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="AT5" t="n">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="AU5" s="3" t="n">
         <v>46191.45833333334</v>
@@ -1329,28 +1329,28 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1361,80 +1361,80 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.48</v>
+        <v>7.5</v>
       </c>
       <c r="O6" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="P6" t="n">
-        <v>6</v>
+        <v>1.44</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.1</v>
+        <v>6.5</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S6" t="n">
         <v>1.41</v>
       </c>
       <c r="T6" t="n">
-        <v>2.48</v>
+        <v>2.59</v>
       </c>
       <c r="U6" t="n">
-        <v>2.91</v>
+        <v>2.8</v>
       </c>
       <c r="V6" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W6" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC6" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG6" t="n">
         <v>1.62</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['88']</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['7']</t>
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.3</v>
+        <v>1.08</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1449,19 +1449,19 @@
         <v>9</v>
       </c>
       <c r="AP6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.24</v>
+        <v>1.09</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.66</v>
+        <v>1.04</v>
       </c>
       <c r="AS6" t="n">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="AT6" t="n">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="AU6" s="3" t="n">
         <v>46191.45833333334</v>
@@ -1488,28 +1488,28 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
         <v>2</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
         <v>1</v>
       </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
         <v>1</v>
@@ -1520,107 +1520,107 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.14</v>
+        <v>1.67</v>
       </c>
       <c r="O7" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="P7" t="n">
-        <v>2.88</v>
+        <v>4.6</v>
       </c>
       <c r="Q7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z7" t="n">
         <v>2.63</v>
       </c>
-      <c r="R7" t="n">
+      <c r="AA7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF7" t="n">
         <v>2.05</v>
       </c>
-      <c r="S7" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AG7" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>['89', '90+5']</t>
+          <t>['50']</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>['53']</t>
+          <t>['45+2', '61']</t>
         </is>
       </c>
       <c r="AJ7" t="n">
         <v>1.3</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AN7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AO7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AP7" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.95</v>
+        <v>1.65</v>
       </c>
       <c r="AS7" t="n">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="AT7" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AU7" s="3" t="n">
         <v>46191.45833333334</v>
@@ -1637,41 +1637,41 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
         <v>2</v>
       </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1679,107 +1679,107 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.67</v>
+        <v>2.45</v>
       </c>
       <c r="O8" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="P8" t="n">
-        <v>4.6</v>
+        <v>2.37</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.25</v>
+        <v>3.4</v>
       </c>
       <c r="R8" t="n">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="S8" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="T8" t="n">
-        <v>2.44</v>
+        <v>2.8</v>
       </c>
       <c r="U8" t="n">
-        <v>3.18</v>
+        <v>2.48</v>
       </c>
       <c r="V8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>['5', '28']</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
         <v>1.29</v>
       </c>
-      <c r="W8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y8" t="n">
+      <c r="AK8" t="n">
         <v>1.4</v>
       </c>
-      <c r="Z8" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>['50']</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>['45+2', '61']</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AK8" t="n">
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN8" t="n">
         <v>2</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>6</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>6</v>
       </c>
       <c r="AO8" t="n">
         <v>7</v>
       </c>
       <c r="AP8" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.23</v>
+        <v>1.07</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.65</v>
+        <v>0.92</v>
       </c>
       <c r="AS8" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="AT8" t="n">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="AU8" s="3" t="n">
         <v>46191.45833333334</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,136 +1806,136 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="O9" t="n">
+        <v>6</v>
+      </c>
+      <c r="P9" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>['7', '78']</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN9" t="n">
         <v>3</v>
       </c>
-      <c r="I9" t="n">
-        <v>2</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="N9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="O9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>['12', '15', '49', '66', '79']</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>['1', '37', '90+1']</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>9</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>4</v>
-      </c>
       <c r="AO9" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="AP9" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AQ9" t="n">
-        <v>2.04</v>
+        <v>1.23</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.49</v>
+        <v>1.16</v>
       </c>
       <c r="AS9" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="AT9" t="n">
         <v>62</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,28 +1965,28 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G10" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" t="n">
         <v>3</v>
-      </c>
-      <c r="H10" t="n">
-        <v>2</v>
       </c>
       <c r="I10" t="n">
         <v>2</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L10" t="n">
         <v>1</v>
@@ -1997,107 +1997,107 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.28</v>
+        <v>1.7</v>
       </c>
       <c r="O10" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="P10" t="n">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="R10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U10" t="n">
         <v>2.67</v>
       </c>
-      <c r="S10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="T10" t="n">
+      <c r="V10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>['12', '15', '49', '66', '79']</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>['1', '37', '90+1']</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AN10" t="n">
         <v>4</v>
       </c>
-      <c r="U10" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>['5', '24', '88']</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>['37', '60']</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>6</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>1</v>
-      </c>
       <c r="AO10" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AP10" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.36</v>
+        <v>2.04</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.41</v>
+        <v>1.49</v>
       </c>
       <c r="AS10" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="AT10" t="n">
-        <v>17</v>
+        <v>62</v>
       </c>
       <c r="AU10" s="3" t="n">
         <v>46191.54166666666</v>
@@ -2124,31 +2124,31 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G11" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" t="n">
         <v>2</v>
       </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
       <c r="I11" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" t="n">
         <v>1</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -2156,43 +2156,43 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="O11" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="P11" t="n">
-        <v>8</v>
+        <v>5.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="R11" t="n">
-        <v>2.78</v>
+        <v>2.67</v>
       </c>
       <c r="S11" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z11" t="n">
         <v>4.5</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>5.5</v>
       </c>
       <c r="AA11" t="n">
         <v>1.44</v>
@@ -2201,62 +2201,62 @@
         <v>2.62</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.93</v>
+        <v>2.23</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>['7', '78']</t>
+          <t>['5', '24', '88']</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['37', '60']</t>
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AN11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP11" t="n">
         <v>3</v>
       </c>
-      <c r="AO11" t="n">
-        <v>8</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>8</v>
-      </c>
       <c r="AQ11" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.16</v>
+        <v>0.41</v>
       </c>
       <c r="AS11" t="n">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="AT11" t="n">
-        <v>62</v>
+        <v>17</v>
       </c>
       <c r="AU11" s="3" t="n">
         <v>46191.54166666666</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.84</v>
+        <v>2.12</v>
       </c>
       <c r="O13" t="n">
-        <v>3.3</v>
+        <v>3.16</v>
       </c>
       <c r="P13" t="n">
-        <v>3.58</v>
+        <v>3.35</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="R13" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="S13" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="T13" t="n">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="U13" t="n">
-        <v>2.98</v>
+        <v>2.82</v>
       </c>
       <c r="V13" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE13" t="n">
         <v>1.05</v>
       </c>
-      <c r="Y13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AF13" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.92</v>
+        <v>1.67</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.12</v>
+        <v>1.84</v>
       </c>
       <c r="O14" t="n">
-        <v>3.16</v>
+        <v>3.3</v>
       </c>
       <c r="P14" t="n">
-        <v>3.35</v>
+        <v>3.58</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="R14" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="S14" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="T14" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="U14" t="n">
-        <v>2.82</v>
+        <v>2.98</v>
       </c>
       <c r="V14" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X14" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.77</v>
+        <v>3.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.67</v>
+        <v>1.92</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>

--- a/jogos_2026-06-18.xlsx
+++ b/jogos_2026-06-18.xlsx
@@ -1011,31 +1011,31 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1043,107 +1043,107 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="O4" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="P4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>['50']</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>['45+2', '61']</t>
+        </is>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
         <v>6</v>
       </c>
-      <c r="Q4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB4" t="n">
+      <c r="AN4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AR4" t="n">
         <v>1.65</v>
       </c>
-      <c r="AC4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0.66</v>
-      </c>
       <c r="AS4" t="n">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="AT4" t="n">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="AU4" s="3" t="n">
         <v>46191.45833333334</v>
@@ -1170,16 +1170,16 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1202,31 +1202,31 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.14</v>
+        <v>7.5</v>
       </c>
       <c r="O5" t="n">
-        <v>3.05</v>
+        <v>3.9</v>
       </c>
       <c r="P5" t="n">
-        <v>2.88</v>
+        <v>1.44</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.63</v>
+        <v>6.5</v>
       </c>
       <c r="R5" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="S5" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="T5" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="U5" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="V5" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W5" t="n">
         <v>1.05</v>
@@ -1235,56 +1235,56 @@
         <v>1.06</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z5" t="n">
         <v>3</v>
       </c>
       <c r="AA5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF5" t="n">
         <v>2.15</v>
       </c>
-      <c r="AB5" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AG5" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>['89', '90+5']</t>
+          <t>['88']</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>['53']</t>
+          <t>['7']</t>
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.57</v>
+        <v>1.08</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AN5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO5" t="n">
         <v>9</v>
@@ -1293,16 +1293,16 @@
         <v>7</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.34</v>
+        <v>1.09</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.95</v>
+        <v>1.04</v>
       </c>
       <c r="AS5" t="n">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="AT5" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="AU5" s="3" t="n">
         <v>46191.45833333334</v>
@@ -1329,16 +1329,16 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
         <v>1</v>
@@ -1347,45 +1347,45 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" t="n">
         <v>1</v>
       </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>7.5</v>
+        <v>2.14</v>
       </c>
       <c r="O6" t="n">
-        <v>3.9</v>
+        <v>3.05</v>
       </c>
       <c r="P6" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S6" t="n">
         <v>1.44</v>
       </c>
-      <c r="Q6" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.41</v>
-      </c>
       <c r="T6" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="U6" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="V6" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W6" t="n">
         <v>1.05</v>
@@ -1394,56 +1394,56 @@
         <v>1.06</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z6" t="n">
         <v>3</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.6</v>
+        <v>3.74</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>['88']</t>
+          <t>['89', '90+5']</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>['7']</t>
+          <t>['53']</t>
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.08</v>
+        <v>1.57</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
       </c>
       <c r="AM6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN6" t="n">
         <v>2</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>3</v>
       </c>
       <c r="AO6" t="n">
         <v>9</v>
@@ -1452,16 +1452,16 @@
         <v>7</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.09</v>
+        <v>1.34</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.04</v>
+        <v>0.95</v>
       </c>
       <c r="AS6" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="AT6" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="AU6" s="3" t="n">
         <v>46191.45833333334</v>
@@ -1488,139 +1488,139 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P7" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
         <v>2</v>
       </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="N7" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="O7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>['50']</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>['45+2', '61']</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>6</v>
-      </c>
       <c r="AN7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AO7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AP7" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.65</v>
+        <v>0.66</v>
       </c>
       <c r="AS7" t="n">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="AT7" t="n">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="AU7" s="3" t="n">
         <v>46191.45833333334</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,28 +1965,28 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
         <v>2</v>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
         <v>1</v>
@@ -1997,107 +1997,107 @@
         </is>
       </c>
       <c r="N10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="O10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="Q10" t="n">
         <v>1.7</v>
       </c>
-      <c r="O10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG10" t="n">
         <v>2.2</v>
       </c>
-      <c r="R10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X10" t="n">
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>['5', '24', '88']</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>['37', '60']</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AN10" t="n">
         <v>1</v>
       </c>
-      <c r="Y10" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>['12', '15', '49', '66', '79']</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>['1', '37', '90+1']</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>9</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>4</v>
-      </c>
       <c r="AO10" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AP10" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="AQ10" t="n">
-        <v>2.04</v>
+        <v>1.36</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.49</v>
+        <v>0.41</v>
       </c>
       <c r="AS10" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="AT10" t="n">
-        <v>62</v>
+        <v>17</v>
       </c>
       <c r="AU10" s="3" t="n">
         <v>46191.54166666666</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,28 +2124,28 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G11" t="n">
+        <v>5</v>
+      </c>
+      <c r="H11" t="n">
         <v>3</v>
-      </c>
-      <c r="H11" t="n">
-        <v>2</v>
       </c>
       <c r="I11" t="n">
         <v>2</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L11" t="n">
         <v>1</v>
@@ -2156,107 +2156,107 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.28</v>
+        <v>1.7</v>
       </c>
       <c r="O11" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="P11" t="n">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="R11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U11" t="n">
         <v>2.67</v>
       </c>
-      <c r="S11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="T11" t="n">
+      <c r="V11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>['12', '15', '49', '66', '79']</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>['1', '37', '90+1']</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AN11" t="n">
         <v>4</v>
       </c>
-      <c r="U11" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>['5', '24', '88']</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>['37', '60']</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>3</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>6</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>1</v>
-      </c>
       <c r="AO11" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AP11" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.36</v>
+        <v>2.04</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.41</v>
+        <v>1.49</v>
       </c>
       <c r="AS11" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="AT11" t="n">
-        <v>17</v>
+        <v>62</v>
       </c>
       <c r="AU11" s="3" t="n">
         <v>46191.54166666666</v>
